--- a/10k_financial_statements.xlsx
+++ b/10k_financial_statements.xlsx
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'AMD - Income statement'!$A$3:$J$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Intel - Balance sheet'!$A$3:$I$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Intel - Cash flow statement'!$A$3:$J$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Intel - Income statement'!$A$3:$J$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Intel - Income statement'!$A$3:$J$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'NVIDIA - Balance sheet'!$A$3:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'NVIDIA - Cash flow statement'!$A$3:$K$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'NVIDIA - Income statement'!$A$3:$K$16</definedName>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="86">
   <si>
     <t>Line item</t>
   </si>
@@ -62,192 +62,195 @@
     <t>FY 2018</t>
   </si>
   <si>
+    <t>Cash and cash equivalents</t>
+  </si>
+  <si>
+    <t>Marketable securities</t>
+  </si>
+  <si>
+    <t>Short-term investments</t>
+  </si>
+  <si>
+    <t>Accounts receivable</t>
+  </si>
+  <si>
+    <t>Inventories</t>
+  </si>
+  <si>
+    <t>Prepaid expenses and other current assets</t>
+  </si>
+  <si>
+    <t>Total current assets</t>
+  </si>
+  <si>
+    <t>Property, plant and equipment</t>
+  </si>
+  <si>
+    <t>Operating lease right-of-use assets</t>
+  </si>
+  <si>
+    <t>Goodwill</t>
+  </si>
+  <si>
+    <t>Other assets</t>
+  </si>
+  <si>
+    <t>Total assets</t>
+  </si>
+  <si>
     <t>Accounts payable</t>
   </si>
   <si>
-    <t>Accounts receivable</t>
+    <t>Other current liabilities</t>
+  </si>
+  <si>
+    <t>Current portion of long-term debt</t>
+  </si>
+  <si>
+    <t>Short-term debt</t>
+  </si>
+  <si>
+    <t>Total current liabilities</t>
+  </si>
+  <si>
+    <t>Long-term debt</t>
+  </si>
+  <si>
+    <t>Other long-term liabilities</t>
+  </si>
+  <si>
+    <t>Common stock</t>
+  </si>
+  <si>
+    <t>Additional paid-in capital</t>
+  </si>
+  <si>
+    <t>Treasury stock</t>
+  </si>
+  <si>
+    <t>Accumulated other comprehensive income</t>
   </si>
   <si>
     <t>Accumulated deficit</t>
   </si>
   <si>
-    <t>Accumulated other comprehensive income</t>
-  </si>
-  <si>
-    <t>Additional paid-in capital</t>
-  </si>
-  <si>
-    <t>Cash and cash equivalents</t>
-  </si>
-  <si>
-    <t>Common stock</t>
-  </si>
-  <si>
-    <t>Current portion of long-term debt</t>
-  </si>
-  <si>
-    <t>Goodwill</t>
-  </si>
-  <si>
-    <t>Inventories</t>
-  </si>
-  <si>
-    <t>Long-term debt</t>
-  </si>
-  <si>
-    <t>Marketable securities</t>
-  </si>
-  <si>
-    <t>Operating lease right-of-use assets</t>
-  </si>
-  <si>
-    <t>Other assets</t>
-  </si>
-  <si>
-    <t>Other current liabilities</t>
-  </si>
-  <si>
-    <t>Other long-term liabilities</t>
-  </si>
-  <si>
-    <t>Prepaid expenses and other current assets</t>
-  </si>
-  <si>
-    <t>Property, plant and equipment</t>
+    <t>Retained earnings</t>
+  </si>
+  <si>
+    <t>Stockholders' equity</t>
+  </si>
+  <si>
+    <t>Total liabilities and equity</t>
   </si>
   <si>
     <t>Receivables from related parties</t>
   </si>
   <si>
-    <t>Retained earnings</t>
-  </si>
-  <si>
-    <t>Short-term debt</t>
-  </si>
-  <si>
-    <t>Short-term investments</t>
-  </si>
-  <si>
-    <t>Stockholders' equity</t>
-  </si>
-  <si>
-    <t>Total assets</t>
-  </si>
-  <si>
-    <t>Total current assets</t>
-  </si>
-  <si>
-    <t>Total current liabilities</t>
-  </si>
-  <si>
-    <t>Total liabilities and equity</t>
-  </si>
-  <si>
-    <t>Treasury stock</t>
-  </si>
-  <si>
     <t>AMD - Balance sheet</t>
   </si>
   <si>
     <t>FY 2017</t>
   </si>
   <si>
+    <t>Revenue</t>
+  </si>
+  <si>
+    <t>Cost of sales</t>
+  </si>
+  <si>
+    <t>Total cost of sales</t>
+  </si>
+  <si>
+    <t>Gross profit</t>
+  </si>
+  <si>
+    <t>Research and development</t>
+  </si>
+  <si>
+    <t>Marketing, general and administrative</t>
+  </si>
+  <si>
     <t>Amortization of acquisition-related intangibles</t>
   </si>
   <si>
+    <t>Licensing gain</t>
+  </si>
+  <si>
+    <t>Total operating expenses</t>
+  </si>
+  <si>
+    <t>Operating income</t>
+  </si>
+  <si>
+    <t>Interest expense</t>
+  </si>
+  <si>
+    <t>Income before income taxes and equity income</t>
+  </si>
+  <si>
+    <t>Income before income taxes</t>
+  </si>
+  <si>
+    <t>Equity income in investee</t>
+  </si>
+  <si>
+    <t>Net income</t>
+  </si>
+  <si>
     <t>Basic EPS</t>
   </si>
   <si>
-    <t>Cost of sales</t>
-  </si>
-  <si>
     <t>Diluted EPS</t>
   </si>
   <si>
-    <t>Equity income in investee</t>
-  </si>
-  <si>
-    <t>Gross profit</t>
-  </si>
-  <si>
-    <t>Income before income taxes</t>
-  </si>
-  <si>
-    <t>Income before income taxes and equity income</t>
-  </si>
-  <si>
-    <t>Interest expense</t>
-  </si>
-  <si>
-    <t>Licensing gain</t>
-  </si>
-  <si>
-    <t>Marketing, general and administrative</t>
-  </si>
-  <si>
-    <t>Net income</t>
-  </si>
-  <si>
-    <t>Operating income</t>
-  </si>
-  <si>
-    <t>Research and development</t>
-  </si>
-  <si>
-    <t>Revenue</t>
-  </si>
-  <si>
-    <t>Total cost of sales</t>
-  </si>
-  <si>
-    <t>Total operating expenses</t>
-  </si>
-  <si>
     <t>AMD - Income statement</t>
   </si>
   <si>
+    <t>Depreciation and amortization</t>
+  </si>
+  <si>
+    <t>Stock-based compensation</t>
+  </si>
+  <si>
+    <t>Deferred income taxes</t>
+  </si>
+  <si>
+    <t>Operating cash flow</t>
+  </si>
+  <si>
     <t>Capital expenditures</t>
   </si>
   <si>
-    <t>Deferred income taxes</t>
-  </si>
-  <si>
-    <t>Depreciation and amortization</t>
+    <t>Investing cash flow</t>
+  </si>
+  <si>
+    <t>Net change in cash</t>
   </si>
   <si>
     <t>Financing cash flow</t>
   </si>
   <si>
-    <t>Investing cash flow</t>
-  </si>
-  <si>
-    <t>Net change in cash</t>
-  </si>
-  <si>
-    <t>Operating cash flow</t>
-  </si>
-  <si>
-    <t>Stock-based compensation</t>
-  </si>
-  <si>
     <t>AMD - Cash flow statement</t>
   </si>
   <si>
     <t>Intangible assets</t>
   </si>
   <si>
+    <t>Total liabilities</t>
+  </si>
+  <si>
     <t>Preferred stock</t>
   </si>
   <si>
-    <t>Total liabilities</t>
-  </si>
-  <si>
     <t>Intel - Balance sheet</t>
   </si>
   <si>
     <t>Income before taxes</t>
   </si>
   <si>
+    <t>Net income attributable to non-controlling interests</t>
+  </si>
+  <si>
     <t>Intel - Income statement</t>
   </si>
   <si>
@@ -260,25 +263,25 @@
     <t>FY 2026</t>
   </si>
   <si>
+    <t>Operating lease assets</t>
+  </si>
+  <si>
+    <t>Deferred income tax assets</t>
+  </si>
+  <si>
     <t>Accrued and other current liabilities</t>
   </si>
   <si>
-    <t>Deferred income tax assets</t>
-  </si>
-  <si>
-    <t>Operating lease assets</t>
-  </si>
-  <si>
     <t>NVIDIA - Balance sheet</t>
   </si>
   <si>
     <t>Cost of revenue</t>
   </si>
   <si>
+    <t>Interest income</t>
+  </si>
+  <si>
     <t>Income tax expense</t>
-  </si>
-  <si>
-    <t>Interest income</t>
   </si>
   <si>
     <t>NVIDIA - Income statement</t>
@@ -297,7 +300,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00;[Red](#,##0.00)"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -321,6 +324,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -336,7 +347,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -344,15 +355,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -694,94 +715,94 @@
         <v>9</v>
       </c>
       <c r="B4" s="1">
-        <v>2929</v>
+        <v>5539</v>
       </c>
       <c r="C4" s="1">
-        <v>1990</v>
+        <v>3787</v>
       </c>
       <c r="D4" s="1">
-        <v>2055</v>
+        <v>3933</v>
       </c>
       <c r="E4" s="1">
-        <v>2493</v>
+        <v>4835</v>
       </c>
       <c r="F4" s="1">
-        <v>1321</v>
+        <v>2535</v>
       </c>
       <c r="G4" s="1">
-        <v>468</v>
+        <v>1595</v>
       </c>
       <c r="H4" s="1">
-        <v>988</v>
+        <v>1466</v>
       </c>
       <c r="I4" s="1">
-        <v>834</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="1">
-        <v>6315</v>
-      </c>
-      <c r="C5" s="1">
-        <v>6192</v>
-      </c>
-      <c r="D5" s="1">
-        <v>5376</v>
-      </c>
-      <c r="E5" s="1">
-        <v>4126</v>
-      </c>
-      <c r="F5" s="1">
-        <v>2706</v>
-      </c>
-      <c r="G5" s="1">
-        <v>2066</v>
-      </c>
       <c r="H5" s="1">
-        <v>1859</v>
+        <v>37</v>
       </c>
       <c r="I5" s="1">
-        <v>1235</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
         <v>11</v>
       </c>
+      <c r="B6" s="1">
+        <v>5013</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1345</v>
+      </c>
       <c r="D6" s="1">
-        <v>723</v>
+        <v>1840</v>
       </c>
       <c r="E6" s="1">
-        <v>-131</v>
+        <v>1020</v>
       </c>
       <c r="F6" s="1">
-        <v>-1451</v>
+        <v>1073</v>
       </c>
       <c r="G6" s="1">
-        <v>-4605</v>
+        <v>695</v>
       </c>
       <c r="H6" s="1">
-        <v>-7095</v>
-      </c>
-      <c r="I6" s="1">
-        <v>-7436</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
         <v>12</v>
       </c>
+      <c r="B7" s="1">
+        <v>6315</v>
+      </c>
+      <c r="C7" s="1">
+        <v>6192</v>
+      </c>
+      <c r="D7" s="1">
+        <v>5376</v>
+      </c>
+      <c r="E7" s="1">
+        <v>4126</v>
+      </c>
       <c r="F7" s="1">
-        <v>-3</v>
+        <v>2706</v>
       </c>
       <c r="G7" s="1">
-        <v>17</v>
+        <v>2066</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1859</v>
       </c>
       <c r="I7" s="1">
-        <v>-8</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -789,28 +810,28 @@
         <v>13</v>
       </c>
       <c r="B8" s="1">
-        <v>63365</v>
+        <v>7920</v>
       </c>
       <c r="C8" s="1">
-        <v>61362</v>
+        <v>5734</v>
       </c>
       <c r="D8" s="1">
-        <v>59676</v>
+        <v>4351</v>
       </c>
       <c r="E8" s="1">
-        <v>58005</v>
+        <v>3771</v>
       </c>
       <c r="F8" s="1">
-        <v>11069</v>
+        <v>1955</v>
       </c>
       <c r="G8" s="1">
-        <v>10544</v>
+        <v>1399</v>
       </c>
       <c r="H8" s="1">
-        <v>9963</v>
+        <v>982</v>
       </c>
       <c r="I8" s="1">
-        <v>8750</v>
+        <v>845</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -818,57 +839,57 @@
         <v>14</v>
       </c>
       <c r="B9" s="1">
-        <v>5539</v>
+        <v>2160</v>
       </c>
       <c r="C9" s="1">
-        <v>3787</v>
+        <v>1878</v>
       </c>
       <c r="D9" s="1">
-        <v>3933</v>
+        <v>1259</v>
       </c>
       <c r="E9" s="1">
-        <v>4835</v>
+        <v>1265</v>
       </c>
       <c r="F9" s="1">
-        <v>2535</v>
+        <v>312</v>
       </c>
       <c r="G9" s="1">
-        <v>1595</v>
+        <v>378</v>
       </c>
       <c r="H9" s="1">
-        <v>1466</v>
+        <v>233</v>
       </c>
       <c r="I9" s="1">
-        <v>1078</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" s="4" customFormat="1">
+      <c r="A10" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="1">
-        <v>17</v>
-      </c>
-      <c r="C10" s="1">
-        <v>17</v>
-      </c>
-      <c r="D10" s="1">
-        <v>17</v>
-      </c>
-      <c r="E10" s="1">
-        <v>16</v>
-      </c>
-      <c r="F10" s="1">
-        <v>12</v>
-      </c>
-      <c r="G10" s="1">
-        <v>12</v>
-      </c>
-      <c r="H10" s="1">
-        <v>12</v>
-      </c>
-      <c r="I10" s="1">
-        <v>10</v>
+      <c r="B10" s="4">
+        <v>26947</v>
+      </c>
+      <c r="C10" s="4">
+        <v>19049</v>
+      </c>
+      <c r="D10" s="4">
+        <v>16768</v>
+      </c>
+      <c r="E10" s="4">
+        <v>15019</v>
+      </c>
+      <c r="F10" s="4">
+        <v>8583</v>
+      </c>
+      <c r="G10" s="4">
+        <v>6143</v>
+      </c>
+      <c r="H10" s="4">
+        <v>4597</v>
+      </c>
+      <c r="I10" s="4">
+        <v>3540</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -876,51 +897,54 @@
         <v>16</v>
       </c>
       <c r="B11" s="1">
-        <v>874</v>
+        <v>2312</v>
       </c>
       <c r="C11" s="1">
-        <v>0</v>
+        <v>1802</v>
       </c>
       <c r="D11" s="1">
-        <v>751</v>
+        <v>1589</v>
       </c>
       <c r="E11" s="1">
-        <v>0</v>
+        <v>1513</v>
       </c>
       <c r="F11" s="1">
-        <v>312</v>
+        <v>702</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>641</v>
+      </c>
+      <c r="H11" s="1">
+        <v>500</v>
+      </c>
+      <c r="I11" s="1">
+        <v>348</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="1">
-        <v>25126</v>
-      </c>
       <c r="C12" s="1">
-        <v>24839</v>
+        <v>623</v>
       </c>
       <c r="D12" s="1">
-        <v>24262</v>
+        <v>633</v>
       </c>
       <c r="E12" s="1">
-        <v>24177</v>
+        <v>460</v>
       </c>
       <c r="F12" s="1">
-        <v>289</v>
+        <v>367</v>
       </c>
       <c r="G12" s="1">
-        <v>289</v>
+        <v>208</v>
       </c>
       <c r="H12" s="1">
-        <v>289</v>
+        <v>205</v>
       </c>
       <c r="I12" s="1">
-        <v>289</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -928,102 +952,126 @@
         <v>18</v>
       </c>
       <c r="B13" s="1">
-        <v>7920</v>
+        <v>25126</v>
       </c>
       <c r="C13" s="1">
-        <v>5734</v>
+        <v>24839</v>
       </c>
       <c r="D13" s="1">
-        <v>4351</v>
+        <v>24262</v>
       </c>
       <c r="E13" s="1">
-        <v>3771</v>
+        <v>24177</v>
       </c>
       <c r="F13" s="1">
-        <v>1955</v>
+        <v>289</v>
       </c>
       <c r="G13" s="1">
-        <v>1399</v>
+        <v>289</v>
       </c>
       <c r="H13" s="1">
-        <v>982</v>
+        <v>289</v>
       </c>
       <c r="I13" s="1">
-        <v>845</v>
+        <v>289</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="1">
-        <v>2348</v>
-      </c>
-      <c r="C14" s="1">
-        <v>1721</v>
-      </c>
-      <c r="D14" s="1">
-        <v>1717</v>
-      </c>
-      <c r="E14" s="1">
-        <v>2467</v>
-      </c>
-      <c r="F14" s="1">
-        <v>1</v>
-      </c>
-      <c r="G14" s="1">
-        <v>330</v>
-      </c>
       <c r="H14" s="1">
-        <v>486</v>
+        <v>379</v>
       </c>
       <c r="I14" s="1">
-        <v>1114</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" s="4" customFormat="1">
+      <c r="A15" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H15" s="1">
-        <v>37</v>
-      </c>
-      <c r="I15" s="1">
-        <v>78</v>
+      <c r="B15" s="4">
+        <v>76926</v>
+      </c>
+      <c r="C15" s="4">
+        <v>69226</v>
+      </c>
+      <c r="D15" s="4">
+        <v>67885</v>
+      </c>
+      <c r="E15" s="4">
+        <v>67580</v>
+      </c>
+      <c r="F15" s="4">
+        <v>12419</v>
+      </c>
+      <c r="G15" s="4">
+        <v>8962</v>
+      </c>
+      <c r="H15" s="4">
+        <v>6028</v>
+      </c>
+      <c r="I15" s="4">
+        <v>4556</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
         <v>21</v>
       </c>
+      <c r="B16" s="1">
+        <v>2929</v>
+      </c>
       <c r="C16" s="1">
-        <v>623</v>
+        <v>1990</v>
       </c>
       <c r="D16" s="1">
-        <v>633</v>
+        <v>2055</v>
       </c>
       <c r="E16" s="1">
-        <v>460</v>
+        <v>2493</v>
       </c>
       <c r="F16" s="1">
-        <v>367</v>
+        <v>1321</v>
       </c>
       <c r="G16" s="1">
-        <v>208</v>
+        <v>468</v>
       </c>
       <c r="H16" s="1">
-        <v>205</v>
+        <v>988</v>
+      </c>
+      <c r="I16" s="1">
+        <v>834</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
         <v>22</v>
       </c>
+      <c r="B17" s="1">
+        <v>402</v>
+      </c>
+      <c r="C17" s="1">
+        <v>555</v>
+      </c>
+      <c r="D17" s="1">
+        <v>438</v>
+      </c>
+      <c r="E17" s="1">
+        <v>336</v>
+      </c>
+      <c r="F17" s="1">
+        <v>98</v>
+      </c>
+      <c r="G17" s="1">
+        <v>75</v>
+      </c>
       <c r="H17" s="1">
-        <v>379</v>
+        <v>74</v>
       </c>
       <c r="I17" s="1">
-        <v>321</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1031,86 +1079,62 @@
         <v>23</v>
       </c>
       <c r="B18" s="1">
-        <v>402</v>
+        <v>874</v>
       </c>
       <c r="C18" s="1">
-        <v>555</v>
+        <v>0</v>
       </c>
       <c r="D18" s="1">
-        <v>438</v>
+        <v>751</v>
       </c>
       <c r="E18" s="1">
-        <v>336</v>
+        <v>0</v>
       </c>
       <c r="F18" s="1">
-        <v>98</v>
+        <v>312</v>
       </c>
       <c r="G18" s="1">
-        <v>75</v>
-      </c>
-      <c r="H18" s="1">
-        <v>74</v>
-      </c>
-      <c r="I18" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="1">
-        <v>1186</v>
-      </c>
-      <c r="C19" s="1">
-        <v>1816</v>
-      </c>
-      <c r="D19" s="1">
-        <v>1850</v>
-      </c>
-      <c r="E19" s="1">
-        <v>1664</v>
-      </c>
-      <c r="F19" s="1">
-        <v>333</v>
-      </c>
-      <c r="G19" s="1">
-        <v>177</v>
-      </c>
       <c r="H19" s="1">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="I19" s="1">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" s="4" customFormat="1">
+      <c r="A20" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="1">
-        <v>2160</v>
-      </c>
-      <c r="C20" s="1">
-        <v>1878</v>
-      </c>
-      <c r="D20" s="1">
-        <v>1259</v>
-      </c>
-      <c r="E20" s="1">
-        <v>1265</v>
-      </c>
-      <c r="F20" s="1">
-        <v>312</v>
-      </c>
-      <c r="G20" s="1">
-        <v>378</v>
-      </c>
-      <c r="H20" s="1">
-        <v>233</v>
-      </c>
-      <c r="I20" s="1">
-        <v>270</v>
+      <c r="B20" s="4">
+        <v>9455</v>
+      </c>
+      <c r="C20" s="4">
+        <v>7281</v>
+      </c>
+      <c r="D20" s="4">
+        <v>6689</v>
+      </c>
+      <c r="E20" s="4">
+        <v>6369</v>
+      </c>
+      <c r="F20" s="4">
+        <v>4240</v>
+      </c>
+      <c r="G20" s="4">
+        <v>2417</v>
+      </c>
+      <c r="H20" s="4">
+        <v>2359</v>
+      </c>
+      <c r="I20" s="4">
+        <v>1984</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1118,51 +1142,57 @@
         <v>26</v>
       </c>
       <c r="B21" s="1">
-        <v>2312</v>
+        <v>2348</v>
       </c>
       <c r="C21" s="1">
-        <v>1802</v>
+        <v>1721</v>
       </c>
       <c r="D21" s="1">
-        <v>1589</v>
+        <v>1717</v>
       </c>
       <c r="E21" s="1">
-        <v>1513</v>
+        <v>2467</v>
       </c>
       <c r="F21" s="1">
-        <v>702</v>
+        <v>1</v>
       </c>
       <c r="G21" s="1">
-        <v>641</v>
+        <v>330</v>
       </c>
       <c r="H21" s="1">
-        <v>500</v>
+        <v>486</v>
       </c>
       <c r="I21" s="1">
-        <v>348</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">
         <v>27</v>
       </c>
+      <c r="B22" s="1">
+        <v>1186</v>
+      </c>
       <c r="C22" s="1">
-        <v>113</v>
+        <v>1816</v>
       </c>
       <c r="D22" s="1">
-        <v>9</v>
+        <v>1850</v>
       </c>
       <c r="E22" s="1">
-        <v>2</v>
+        <v>1664</v>
       </c>
       <c r="F22" s="1">
-        <v>2</v>
+        <v>333</v>
       </c>
       <c r="G22" s="1">
-        <v>10</v>
+        <v>177</v>
       </c>
       <c r="H22" s="1">
-        <v>20</v>
+        <v>157</v>
+      </c>
+      <c r="I22" s="1">
+        <v>192</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1170,24 +1200,57 @@
         <v>28</v>
       </c>
       <c r="B23" s="1">
-        <v>6699</v>
+        <v>17</v>
       </c>
       <c r="C23" s="1">
-        <v>2364</v>
+        <v>17</v>
       </c>
       <c r="D23" s="1">
-        <v>723</v>
+        <v>17</v>
+      </c>
+      <c r="E23" s="1">
+        <v>16</v>
+      </c>
+      <c r="F23" s="1">
+        <v>12</v>
+      </c>
+      <c r="G23" s="1">
+        <v>12</v>
+      </c>
+      <c r="H23" s="1">
+        <v>12</v>
+      </c>
+      <c r="I23" s="1">
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" t="s">
         <v>29</v>
       </c>
+      <c r="B24" s="1">
+        <v>63365</v>
+      </c>
+      <c r="C24" s="1">
+        <v>61362</v>
+      </c>
+      <c r="D24" s="1">
+        <v>59676</v>
+      </c>
+      <c r="E24" s="1">
+        <v>58005</v>
+      </c>
+      <c r="F24" s="1">
+        <v>11069</v>
+      </c>
+      <c r="G24" s="1">
+        <v>10544</v>
+      </c>
       <c r="H24" s="1">
-        <v>0</v>
+        <v>9963</v>
       </c>
       <c r="I24" s="1">
-        <v>136</v>
+        <v>8750</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1195,83 +1258,68 @@
         <v>30</v>
       </c>
       <c r="B25" s="1">
-        <v>5013</v>
+        <v>65</v>
       </c>
       <c r="C25" s="1">
-        <v>1345</v>
+        <v>58</v>
       </c>
       <c r="D25" s="1">
-        <v>1840</v>
+        <v>47</v>
       </c>
       <c r="E25" s="1">
-        <v>1020</v>
+        <v>33</v>
       </c>
       <c r="F25" s="1">
-        <v>1073</v>
+        <v>25</v>
       </c>
       <c r="G25" s="1">
-        <v>695</v>
+        <v>6</v>
       </c>
       <c r="H25" s="1">
-        <v>37</v>
+        <v>-53</v>
+      </c>
+      <c r="I25" s="1">
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" t="s">
         <v>31</v>
       </c>
-      <c r="B26" s="1">
-        <v>62999</v>
-      </c>
-      <c r="C26" s="1">
-        <v>57568</v>
-      </c>
-      <c r="D26" s="1">
-        <v>55892</v>
-      </c>
-      <c r="E26" s="1">
-        <v>54750</v>
-      </c>
       <c r="F26" s="1">
-        <v>7497</v>
+        <v>-3</v>
       </c>
       <c r="G26" s="1">
-        <v>5837</v>
+        <v>17</v>
       </c>
       <c r="H26" s="1">
-        <v>2827</v>
+        <v>0</v>
       </c>
       <c r="I26" s="1">
-        <v>1266</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" t="s">
         <v>32</v>
       </c>
-      <c r="B27" s="1">
-        <v>76926</v>
-      </c>
-      <c r="C27" s="1">
-        <v>69226</v>
-      </c>
       <c r="D27" s="1">
-        <v>67885</v>
+        <v>723</v>
       </c>
       <c r="E27" s="1">
-        <v>67580</v>
+        <v>-131</v>
       </c>
       <c r="F27" s="1">
-        <v>12419</v>
+        <v>-1451</v>
       </c>
       <c r="G27" s="1">
-        <v>8962</v>
+        <v>-4605</v>
       </c>
       <c r="H27" s="1">
-        <v>6028</v>
+        <v>-7095</v>
       </c>
       <c r="I27" s="1">
-        <v>4556</v>
+        <v>-7436</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1279,85 +1327,70 @@
         <v>33</v>
       </c>
       <c r="B28" s="1">
-        <v>26947</v>
+        <v>6699</v>
       </c>
       <c r="C28" s="1">
-        <v>19049</v>
+        <v>2364</v>
       </c>
       <c r="D28" s="1">
-        <v>16768</v>
-      </c>
-      <c r="E28" s="1">
-        <v>15019</v>
-      </c>
-      <c r="F28" s="1">
-        <v>8583</v>
-      </c>
-      <c r="G28" s="1">
-        <v>6143</v>
-      </c>
-      <c r="H28" s="1">
-        <v>4597</v>
-      </c>
-      <c r="I28" s="1">
-        <v>3540</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="A29" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" s="4" customFormat="1">
+      <c r="A29" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="1">
-        <v>9455</v>
-      </c>
-      <c r="C29" s="1">
-        <v>7281</v>
-      </c>
-      <c r="D29" s="1">
-        <v>6689</v>
-      </c>
-      <c r="E29" s="1">
-        <v>6369</v>
-      </c>
-      <c r="F29" s="1">
-        <v>4240</v>
-      </c>
-      <c r="G29" s="1">
-        <v>2417</v>
-      </c>
-      <c r="H29" s="1">
-        <v>2359</v>
-      </c>
-      <c r="I29" s="1">
-        <v>1984</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="A30" t="s">
+      <c r="B29" s="4">
+        <v>62999</v>
+      </c>
+      <c r="C29" s="4">
+        <v>57568</v>
+      </c>
+      <c r="D29" s="4">
+        <v>55892</v>
+      </c>
+      <c r="E29" s="4">
+        <v>54750</v>
+      </c>
+      <c r="F29" s="4">
+        <v>7497</v>
+      </c>
+      <c r="G29" s="4">
+        <v>5837</v>
+      </c>
+      <c r="H29" s="4">
+        <v>2827</v>
+      </c>
+      <c r="I29" s="4">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" s="4" customFormat="1">
+      <c r="A30" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B30" s="4">
         <v>76926</v>
       </c>
-      <c r="C30" s="1">
+      <c r="C30" s="4">
         <v>69226</v>
       </c>
-      <c r="D30" s="1">
+      <c r="D30" s="4">
         <v>67885</v>
       </c>
-      <c r="E30" s="1">
+      <c r="E30" s="4">
         <v>67580</v>
       </c>
-      <c r="F30" s="1">
+      <c r="F30" s="4">
         <v>12419</v>
       </c>
-      <c r="G30" s="1">
+      <c r="G30" s="4">
         <v>8962</v>
       </c>
-      <c r="H30" s="1">
+      <c r="H30" s="4">
         <v>6028</v>
       </c>
-      <c r="I30" s="1">
+      <c r="I30" s="4">
         <v>4556</v>
       </c>
     </row>
@@ -1365,29 +1398,23 @@
       <c r="A31" t="s">
         <v>36</v>
       </c>
-      <c r="B31" s="1">
-        <v>65</v>
-      </c>
       <c r="C31" s="1">
-        <v>58</v>
+        <v>113</v>
       </c>
       <c r="D31" s="1">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="E31" s="1">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="F31" s="1">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="G31" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H31" s="1">
-        <v>5</v>
-      </c>
-      <c r="I31" s="1">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1448,16 +1475,31 @@
         <v>39</v>
       </c>
       <c r="B4" s="1">
-        <v>1031</v>
+        <v>34639</v>
       </c>
       <c r="C4" s="1">
-        <v>946</v>
+        <v>25785</v>
       </c>
       <c r="D4" s="1">
-        <v>942</v>
+        <v>22680</v>
       </c>
       <c r="E4" s="1">
-        <v>1448</v>
+        <v>23601</v>
+      </c>
+      <c r="F4" s="1">
+        <v>16434</v>
+      </c>
+      <c r="G4" s="1">
+        <v>9763</v>
+      </c>
+      <c r="H4" s="1">
+        <v>6731</v>
+      </c>
+      <c r="I4" s="1">
+        <v>6475</v>
+      </c>
+      <c r="J4" s="1">
+        <v>5253</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1465,95 +1507,86 @@
         <v>40</v>
       </c>
       <c r="B5" s="1">
-        <v>2.63</v>
+        <v>16456</v>
       </c>
       <c r="C5" s="1">
-        <v>1.01</v>
+        <v>12114</v>
       </c>
       <c r="D5" s="1">
-        <v>0.53</v>
+        <v>11278</v>
       </c>
       <c r="E5" s="1">
-        <v>0.85</v>
+        <v>11550</v>
       </c>
       <c r="F5" s="1">
-        <v>2.61</v>
+        <v>8505</v>
       </c>
       <c r="G5" s="1">
-        <v>2.1</v>
+        <v>5416</v>
       </c>
       <c r="H5" s="1">
-        <v>0.31</v>
+        <v>3863</v>
       </c>
       <c r="I5" s="1">
-        <v>0.34</v>
+        <v>4028</v>
       </c>
       <c r="J5" s="1">
-        <v>-0.03</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
+        <v>3466</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="4" customFormat="1">
+      <c r="A6" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="1">
-        <v>16456</v>
-      </c>
-      <c r="C6" s="1">
-        <v>12114</v>
-      </c>
-      <c r="D6" s="1">
-        <v>11278</v>
-      </c>
-      <c r="E6" s="1">
-        <v>11550</v>
-      </c>
-      <c r="F6" s="1">
+      <c r="B6" s="4">
+        <v>17487</v>
+      </c>
+      <c r="C6" s="4">
+        <v>13060</v>
+      </c>
+      <c r="D6" s="4">
+        <v>12220</v>
+      </c>
+      <c r="E6" s="4">
+        <v>12998</v>
+      </c>
+      <c r="F6" s="4">
         <v>8505</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" s="4">
         <v>5416</v>
       </c>
-      <c r="H6" s="1">
-        <v>3863</v>
-      </c>
-      <c r="I6" s="1">
-        <v>4028</v>
-      </c>
-      <c r="J6" s="1">
-        <v>3466</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
+    </row>
+    <row r="7" spans="1:10" s="4" customFormat="1">
+      <c r="A7" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="1">
-        <v>2.61</v>
-      </c>
-      <c r="C7" s="1">
-        <v>1</v>
-      </c>
-      <c r="D7" s="1">
-        <v>0.53</v>
-      </c>
-      <c r="E7" s="1">
-        <v>0.84</v>
-      </c>
-      <c r="F7" s="1">
-        <v>2.57</v>
-      </c>
-      <c r="G7" s="1">
-        <v>2.06</v>
-      </c>
-      <c r="H7" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="I7" s="1">
-        <v>0.32</v>
-      </c>
-      <c r="J7" s="1">
-        <v>-0.03</v>
+      <c r="B7" s="4">
+        <v>17152</v>
+      </c>
+      <c r="C7" s="4">
+        <v>12725</v>
+      </c>
+      <c r="D7" s="4">
+        <v>10460</v>
+      </c>
+      <c r="E7" s="4">
+        <v>10603</v>
+      </c>
+      <c r="F7" s="4">
+        <v>7929</v>
+      </c>
+      <c r="G7" s="4">
+        <v>4347</v>
+      </c>
+      <c r="H7" s="4">
+        <v>2868</v>
+      </c>
+      <c r="I7" s="4">
+        <v>2447</v>
+      </c>
+      <c r="J7" s="4">
+        <v>1787</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1561,22 +1594,31 @@
         <v>43</v>
       </c>
       <c r="B8" s="1">
-        <v>26</v>
+        <v>8091</v>
       </c>
       <c r="C8" s="1">
-        <v>33</v>
+        <v>6456</v>
       </c>
       <c r="D8" s="1">
-        <v>16</v>
+        <v>5872</v>
       </c>
       <c r="E8" s="1">
-        <v>14</v>
+        <v>5005</v>
       </c>
       <c r="F8" s="1">
-        <v>6</v>
+        <v>2845</v>
       </c>
       <c r="G8" s="1">
-        <v>5</v>
+        <v>1983</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1547</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1434</v>
+      </c>
+      <c r="J8" s="1">
+        <v>1196</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1584,57 +1626,54 @@
         <v>44</v>
       </c>
       <c r="B9" s="1">
-        <v>17152</v>
+        <v>4144</v>
       </c>
       <c r="C9" s="1">
-        <v>12725</v>
+        <v>2783</v>
       </c>
       <c r="D9" s="1">
-        <v>10460</v>
+        <v>2352</v>
       </c>
       <c r="E9" s="1">
-        <v>10603</v>
+        <v>2336</v>
       </c>
       <c r="F9" s="1">
-        <v>7929</v>
+        <v>1448</v>
       </c>
       <c r="G9" s="1">
-        <v>4347</v>
+        <v>995</v>
       </c>
       <c r="H9" s="1">
-        <v>2868</v>
+        <v>750</v>
       </c>
       <c r="I9" s="1">
-        <v>2447</v>
+        <v>562</v>
       </c>
       <c r="J9" s="1">
-        <v>1787</v>
+        <v>516</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>45</v>
       </c>
+      <c r="B10" s="1">
+        <v>1031</v>
+      </c>
       <c r="C10" s="1">
-        <v>2022</v>
+        <v>946</v>
       </c>
       <c r="D10" s="1">
-        <v>508</v>
+        <v>942</v>
       </c>
       <c r="E10" s="1">
-        <v>1198</v>
+        <v>1448</v>
       </c>
       <c r="F10" s="1">
-        <v>3675</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>1275</v>
-      </c>
-      <c r="H10" s="1">
-        <v>372</v>
-      </c>
-      <c r="I10" s="1">
-        <v>330</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1642,80 +1681,92 @@
         <v>46</v>
       </c>
       <c r="C11" s="1">
-        <v>1989</v>
+        <v>-48</v>
       </c>
       <c r="D11" s="1">
-        <v>492</v>
+        <v>-34</v>
       </c>
       <c r="E11" s="1">
-        <v>1184</v>
+        <v>-102</v>
       </c>
       <c r="F11" s="1">
-        <v>3669</v>
+        <v>-12</v>
       </c>
       <c r="G11" s="1">
-        <v>1275</v>
+        <v>0</v>
       </c>
       <c r="H11" s="1">
-        <v>372</v>
+        <v>-60</v>
       </c>
       <c r="I11" s="1">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" t="s">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1">
+        <v>-52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" s="4" customFormat="1">
+      <c r="A12" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B12" s="1">
-        <v>-131</v>
-      </c>
-      <c r="C12" s="1">
-        <v>-92</v>
-      </c>
-      <c r="D12" s="1">
-        <v>-106</v>
-      </c>
-      <c r="E12" s="1">
-        <v>-88</v>
-      </c>
-      <c r="F12" s="1">
-        <v>-34</v>
-      </c>
-      <c r="G12" s="1">
-        <v>-47</v>
-      </c>
-      <c r="H12" s="1">
-        <v>-94</v>
-      </c>
-      <c r="I12" s="1">
-        <v>-121</v>
-      </c>
-      <c r="J12" s="1">
-        <v>-126</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" t="s">
+      <c r="B12" s="4">
+        <v>13458</v>
+      </c>
+      <c r="C12" s="4">
+        <v>10825</v>
+      </c>
+      <c r="D12" s="4">
+        <v>10059</v>
+      </c>
+      <c r="E12" s="4">
+        <v>9339</v>
+      </c>
+      <c r="F12" s="4">
+        <v>4281</v>
+      </c>
+      <c r="G12" s="4">
+        <v>2978</v>
+      </c>
+      <c r="H12" s="4">
+        <v>2237</v>
+      </c>
+      <c r="I12" s="4">
+        <v>1996</v>
+      </c>
+      <c r="J12" s="4">
+        <v>1660</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" s="4" customFormat="1">
+      <c r="A13" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="1">
-        <v>-48</v>
-      </c>
-      <c r="D13" s="1">
-        <v>-34</v>
-      </c>
-      <c r="E13" s="1">
-        <v>-102</v>
-      </c>
-      <c r="F13" s="1">
-        <v>-12</v>
-      </c>
-      <c r="H13" s="1">
-        <v>-60</v>
-      </c>
-      <c r="J13" s="1">
-        <v>-52</v>
+      <c r="B13" s="4">
+        <v>3694</v>
+      </c>
+      <c r="C13" s="4">
+        <v>1900</v>
+      </c>
+      <c r="D13" s="4">
+        <v>401</v>
+      </c>
+      <c r="E13" s="4">
+        <v>1264</v>
+      </c>
+      <c r="F13" s="4">
+        <v>3648</v>
+      </c>
+      <c r="G13" s="4">
+        <v>1369</v>
+      </c>
+      <c r="H13" s="4">
+        <v>631</v>
+      </c>
+      <c r="I13" s="4">
+        <v>451</v>
+      </c>
+      <c r="J13" s="4">
+        <v>127</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -1723,95 +1774,83 @@
         <v>49</v>
       </c>
       <c r="B14" s="1">
-        <v>4144</v>
+        <v>-131</v>
       </c>
       <c r="C14" s="1">
-        <v>2783</v>
+        <v>-92</v>
       </c>
       <c r="D14" s="1">
-        <v>2352</v>
+        <v>-106</v>
       </c>
       <c r="E14" s="1">
-        <v>2336</v>
+        <v>-88</v>
       </c>
       <c r="F14" s="1">
-        <v>1448</v>
+        <v>-34</v>
       </c>
       <c r="G14" s="1">
-        <v>995</v>
+        <v>-47</v>
       </c>
       <c r="H14" s="1">
-        <v>750</v>
+        <v>-94</v>
       </c>
       <c r="I14" s="1">
-        <v>562</v>
+        <v>-121</v>
       </c>
       <c r="J14" s="1">
-        <v>516</v>
+        <v>-126</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>50</v>
       </c>
-      <c r="B15" s="1">
-        <v>4335</v>
-      </c>
       <c r="C15" s="1">
-        <v>1641</v>
+        <v>1989</v>
       </c>
       <c r="D15" s="1">
-        <v>854</v>
+        <v>492</v>
       </c>
       <c r="E15" s="1">
-        <v>1320</v>
+        <v>1184</v>
       </c>
       <c r="F15" s="1">
-        <v>3162</v>
+        <v>3669</v>
       </c>
       <c r="G15" s="1">
-        <v>2490</v>
+        <v>1275</v>
       </c>
       <c r="H15" s="1">
-        <v>341</v>
+        <v>372</v>
       </c>
       <c r="I15" s="1">
-        <v>337</v>
-      </c>
-      <c r="J15" s="1">
-        <v>-33</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" s="4" customFormat="1">
+      <c r="A16" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B16" s="1">
-        <v>3694</v>
-      </c>
-      <c r="C16" s="1">
-        <v>1900</v>
-      </c>
-      <c r="D16" s="1">
-        <v>401</v>
-      </c>
-      <c r="E16" s="1">
-        <v>1264</v>
-      </c>
-      <c r="F16" s="1">
-        <v>3648</v>
-      </c>
-      <c r="G16" s="1">
-        <v>1369</v>
-      </c>
-      <c r="H16" s="1">
-        <v>631</v>
-      </c>
-      <c r="I16" s="1">
-        <v>451</v>
-      </c>
-      <c r="J16" s="1">
-        <v>127</v>
+      <c r="C16" s="4">
+        <v>2022</v>
+      </c>
+      <c r="D16" s="4">
+        <v>508</v>
+      </c>
+      <c r="E16" s="4">
+        <v>1198</v>
+      </c>
+      <c r="F16" s="4">
+        <v>3675</v>
+      </c>
+      <c r="G16" s="4">
+        <v>1275</v>
+      </c>
+      <c r="H16" s="4">
+        <v>372</v>
+      </c>
+      <c r="I16" s="4">
+        <v>330</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -1819,63 +1858,57 @@
         <v>52</v>
       </c>
       <c r="B17" s="1">
-        <v>8091</v>
+        <v>26</v>
       </c>
       <c r="C17" s="1">
-        <v>6456</v>
+        <v>33</v>
       </c>
       <c r="D17" s="1">
-        <v>5872</v>
+        <v>16</v>
       </c>
       <c r="E17" s="1">
-        <v>5005</v>
+        <v>14</v>
       </c>
       <c r="F17" s="1">
-        <v>2845</v>
+        <v>6</v>
       </c>
       <c r="G17" s="1">
-        <v>1983</v>
+        <v>5</v>
       </c>
       <c r="H17" s="1">
-        <v>1547</v>
-      </c>
-      <c r="I17" s="1">
-        <v>1434</v>
-      </c>
-      <c r="J17" s="1">
-        <v>1196</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" s="4" customFormat="1">
+      <c r="A18" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B18" s="1">
-        <v>34639</v>
-      </c>
-      <c r="C18" s="1">
-        <v>25785</v>
-      </c>
-      <c r="D18" s="1">
-        <v>22680</v>
-      </c>
-      <c r="E18" s="1">
-        <v>23601</v>
-      </c>
-      <c r="F18" s="1">
-        <v>16434</v>
-      </c>
-      <c r="G18" s="1">
-        <v>9763</v>
-      </c>
-      <c r="H18" s="1">
-        <v>6731</v>
-      </c>
-      <c r="I18" s="1">
-        <v>6475</v>
-      </c>
-      <c r="J18" s="1">
-        <v>5253</v>
+      <c r="B18" s="4">
+        <v>4335</v>
+      </c>
+      <c r="C18" s="4">
+        <v>1641</v>
+      </c>
+      <c r="D18" s="4">
+        <v>854</v>
+      </c>
+      <c r="E18" s="4">
+        <v>1320</v>
+      </c>
+      <c r="F18" s="4">
+        <v>3162</v>
+      </c>
+      <c r="G18" s="4">
+        <v>2490</v>
+      </c>
+      <c r="H18" s="4">
+        <v>341</v>
+      </c>
+      <c r="I18" s="4">
+        <v>337</v>
+      </c>
+      <c r="J18" s="4">
+        <v>-33</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -1883,22 +1916,31 @@
         <v>54</v>
       </c>
       <c r="B19" s="1">
-        <v>17487</v>
+        <v>2.63</v>
       </c>
       <c r="C19" s="1">
-        <v>13060</v>
+        <v>1.01</v>
       </c>
       <c r="D19" s="1">
-        <v>12220</v>
+        <v>0.53</v>
       </c>
       <c r="E19" s="1">
-        <v>12998</v>
+        <v>0.85</v>
       </c>
       <c r="F19" s="1">
-        <v>8505</v>
+        <v>2.61</v>
       </c>
       <c r="G19" s="1">
-        <v>5416</v>
+        <v>2.1</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0.31</v>
+      </c>
+      <c r="I19" s="1">
+        <v>0.34</v>
+      </c>
+      <c r="J19" s="1">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -1906,31 +1948,31 @@
         <v>55</v>
       </c>
       <c r="B20" s="1">
-        <v>13458</v>
+        <v>2.61</v>
       </c>
       <c r="C20" s="1">
-        <v>10825</v>
+        <v>1</v>
       </c>
       <c r="D20" s="1">
-        <v>10059</v>
+        <v>0.53</v>
       </c>
       <c r="E20" s="1">
-        <v>9339</v>
+        <v>0.84</v>
       </c>
       <c r="F20" s="1">
-        <v>4281</v>
+        <v>2.57</v>
       </c>
       <c r="G20" s="1">
-        <v>2978</v>
+        <v>2.06</v>
       </c>
       <c r="H20" s="1">
-        <v>2237</v>
+        <v>0.3</v>
       </c>
       <c r="I20" s="1">
-        <v>1996</v>
+        <v>0.32</v>
       </c>
       <c r="J20" s="1">
-        <v>1660</v>
+        <v>-0.03</v>
       </c>
     </row>
   </sheetData>
@@ -1986,628 +2028,658 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="1">
-        <v>410</v>
-      </c>
-      <c r="C4" s="1">
-        <v>-109</v>
-      </c>
-      <c r="D4" s="1">
-        <v>-419</v>
-      </c>
-      <c r="E4" s="1">
-        <v>931</v>
-      </c>
-      <c r="F4" s="1">
-        <v>801</v>
-      </c>
-      <c r="G4" s="1">
-        <v>-513</v>
-      </c>
-      <c r="H4" s="1">
-        <v>373</v>
-      </c>
-      <c r="I4" s="1">
-        <v>212</v>
-      </c>
-      <c r="J4" s="1">
-        <v>-8</v>
+    <row r="4" spans="1:10" s="4" customFormat="1">
+      <c r="A4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>4335</v>
+      </c>
+      <c r="C4" s="4">
+        <v>1641</v>
+      </c>
+      <c r="D4" s="4">
+        <v>854</v>
+      </c>
+      <c r="E4" s="4">
+        <v>1320</v>
+      </c>
+      <c r="F4" s="4">
+        <v>3162</v>
+      </c>
+      <c r="G4" s="4">
+        <v>2490</v>
+      </c>
+      <c r="H4" s="4">
+        <v>341</v>
+      </c>
+      <c r="I4" s="4">
+        <v>337</v>
+      </c>
+      <c r="J4" s="4">
+        <v>-33</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="B5" s="1">
-        <v>-121</v>
+        <v>750</v>
       </c>
       <c r="C5" s="1">
-        <v>-1865</v>
+        <v>671</v>
       </c>
       <c r="D5" s="1">
-        <v>-1250</v>
+        <v>3453</v>
       </c>
       <c r="E5" s="1">
-        <v>-1091</v>
+        <v>4174</v>
       </c>
       <c r="F5" s="1">
-        <v>-640</v>
+        <v>407</v>
       </c>
       <c r="G5" s="1">
-        <v>-219</v>
+        <v>312</v>
       </c>
       <c r="H5" s="1">
-        <v>-623</v>
+        <v>222</v>
       </c>
       <c r="I5" s="1">
-        <v>-806</v>
+        <v>170</v>
       </c>
       <c r="J5" s="1">
-        <v>-103</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="B6" s="1">
-        <v>2254</v>
+        <v>1638</v>
       </c>
       <c r="C6" s="1">
-        <v>2393</v>
+        <v>1407</v>
       </c>
       <c r="D6" s="1">
-        <v>2811</v>
+        <v>1384</v>
       </c>
       <c r="E6" s="1">
-        <v>3548</v>
+        <v>1081</v>
+      </c>
+      <c r="F6" s="1">
+        <v>379</v>
+      </c>
+      <c r="G6" s="1">
+        <v>274</v>
+      </c>
+      <c r="H6" s="1">
+        <v>197</v>
+      </c>
+      <c r="I6" s="1">
+        <v>137</v>
+      </c>
+      <c r="J6" s="1">
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B7" s="1">
-        <v>-974</v>
+        <v>248</v>
       </c>
       <c r="C7" s="1">
-        <v>-636</v>
+        <v>-1163</v>
       </c>
       <c r="D7" s="1">
-        <v>-546</v>
+        <v>-1019</v>
       </c>
       <c r="E7" s="1">
-        <v>-450</v>
+        <v>-1505</v>
       </c>
       <c r="F7" s="1">
-        <v>-301</v>
+        <v>308</v>
       </c>
       <c r="G7" s="1">
-        <v>-294</v>
+        <v>-1223</v>
       </c>
       <c r="H7" s="1">
-        <v>-217</v>
+        <v>-4</v>
       </c>
       <c r="I7" s="1">
-        <v>-163</v>
+        <v>-4</v>
       </c>
       <c r="J7" s="1">
-        <v>-113</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B8" s="1">
-        <v>5539</v>
+        <v>-121</v>
       </c>
       <c r="C8" s="1">
-        <v>3787</v>
+        <v>-1865</v>
       </c>
       <c r="D8" s="1">
-        <v>-902</v>
+        <v>-1250</v>
       </c>
       <c r="E8" s="1">
-        <v>2535</v>
+        <v>-1091</v>
       </c>
       <c r="F8" s="1">
-        <v>940</v>
+        <v>-640</v>
       </c>
       <c r="G8" s="1">
-        <v>125</v>
+        <v>-219</v>
       </c>
       <c r="H8" s="1">
-        <v>387</v>
+        <v>-623</v>
       </c>
       <c r="I8" s="1">
-        <v>-108</v>
+        <v>-806</v>
       </c>
       <c r="J8" s="1">
-        <v>-75</v>
+        <v>-103</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B9" s="1">
-        <v>285</v>
+        <v>-2189</v>
       </c>
       <c r="C9" s="1">
-        <v>279</v>
+        <v>-1458</v>
       </c>
       <c r="D9" s="1">
-        <v>268</v>
+        <v>-580</v>
       </c>
       <c r="E9" s="1">
-        <v>167</v>
+        <v>-1401</v>
       </c>
       <c r="F9" s="1">
-        <v>104</v>
+        <v>-556</v>
       </c>
       <c r="G9" s="1">
-        <v>85</v>
+        <v>-417</v>
       </c>
       <c r="H9" s="1">
-        <v>74</v>
+        <v>-137</v>
       </c>
       <c r="I9" s="1">
-        <v>70</v>
+        <v>-151</v>
       </c>
       <c r="J9" s="1">
-        <v>20</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="B10" s="1">
-        <v>248</v>
+        <v>410</v>
       </c>
       <c r="C10" s="1">
-        <v>-1163</v>
+        <v>-109</v>
       </c>
       <c r="D10" s="1">
-        <v>-1019</v>
+        <v>-419</v>
       </c>
       <c r="E10" s="1">
-        <v>-1505</v>
+        <v>931</v>
       </c>
       <c r="F10" s="1">
-        <v>308</v>
+        <v>801</v>
       </c>
       <c r="G10" s="1">
-        <v>-1223</v>
+        <v>-513</v>
       </c>
       <c r="H10" s="1">
-        <v>-4</v>
+        <v>373</v>
       </c>
       <c r="I10" s="1">
-        <v>-4</v>
+        <v>212</v>
+      </c>
+      <c r="J10" s="1">
+        <v>-8</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1">
-        <v>750</v>
+        <v>-11</v>
       </c>
       <c r="C11" s="1">
-        <v>671</v>
+        <v>343</v>
       </c>
       <c r="D11" s="1">
-        <v>3453</v>
+        <v>-472</v>
       </c>
       <c r="E11" s="1">
-        <v>4174</v>
+        <v>-1197</v>
       </c>
       <c r="F11" s="1">
-        <v>407</v>
+        <v>-920</v>
       </c>
       <c r="G11" s="1">
-        <v>312</v>
+        <v>-231</v>
       </c>
       <c r="H11" s="1">
-        <v>222</v>
+        <v>-176</v>
       </c>
       <c r="I11" s="1">
-        <v>170</v>
+        <v>-70</v>
       </c>
       <c r="J11" s="1">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" t="s">
+        <v>-167</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" s="4" customFormat="1">
+      <c r="A12" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B12" s="1">
-        <v>-431</v>
-      </c>
-      <c r="C12" s="1">
-        <v>-2062</v>
-      </c>
-      <c r="D12" s="1">
-        <v>-1146</v>
-      </c>
-      <c r="E12" s="1">
-        <v>-3264</v>
-      </c>
-      <c r="F12" s="1">
-        <v>-1895</v>
-      </c>
-      <c r="G12" s="1">
-        <v>6</v>
-      </c>
-      <c r="H12" s="1">
-        <v>43</v>
-      </c>
-      <c r="I12" s="1">
-        <v>28</v>
+      <c r="B12" s="4">
+        <v>6493</v>
+      </c>
+      <c r="C12" s="4">
+        <v>3041</v>
+      </c>
+      <c r="D12" s="4">
+        <v>1667</v>
+      </c>
+      <c r="E12" s="4">
+        <v>3565</v>
+      </c>
+      <c r="F12" s="4">
+        <v>3521</v>
+      </c>
+      <c r="G12" s="4">
+        <v>1071</v>
+      </c>
+      <c r="H12" s="4">
+        <v>493</v>
+      </c>
+      <c r="I12" s="4">
+        <v>34</v>
+      </c>
+      <c r="J12" s="4">
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="B13" s="1">
-        <v>-2189</v>
+        <v>-974</v>
       </c>
       <c r="C13" s="1">
-        <v>-1458</v>
+        <v>-636</v>
       </c>
       <c r="D13" s="1">
-        <v>-580</v>
+        <v>-546</v>
       </c>
       <c r="E13" s="1">
-        <v>-1401</v>
+        <v>-450</v>
       </c>
       <c r="F13" s="1">
-        <v>-556</v>
+        <v>-301</v>
       </c>
       <c r="G13" s="1">
-        <v>-417</v>
+        <v>-294</v>
       </c>
       <c r="H13" s="1">
-        <v>-137</v>
+        <v>-217</v>
       </c>
       <c r="I13" s="1">
-        <v>-151</v>
+        <v>-163</v>
       </c>
       <c r="J13" s="1">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" t="s">
-        <v>61</v>
-      </c>
-      <c r="B14" s="1">
+        <v>-113</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" s="4" customFormat="1">
+      <c r="A14" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" s="4">
         <v>-6851</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="4">
         <v>-1101</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14" s="4">
         <v>-1423</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F14" s="4">
         <v>-686</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" s="4">
         <v>-952</v>
       </c>
-      <c r="H14" s="1">
+      <c r="H14" s="4">
         <v>-149</v>
       </c>
-      <c r="I14" s="1">
+      <c r="I14" s="4">
         <v>-170</v>
       </c>
-      <c r="J14" s="1">
+      <c r="J14" s="4">
         <v>-54</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
-      <c r="A15" t="s">
-        <v>19</v>
-      </c>
-      <c r="H15" s="1">
-        <v>-403</v>
-      </c>
-      <c r="I15" s="1">
-        <v>-41</v>
-      </c>
-      <c r="J15" s="1">
-        <v>-110</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" t="s">
-        <v>62</v>
-      </c>
-      <c r="E16" s="1">
+    <row r="15" spans="1:10" s="4" customFormat="1">
+      <c r="A15" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E15" s="4">
         <v>2300</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F15" s="4">
         <v>940</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G15" s="4">
         <v>125</v>
       </c>
-      <c r="H16" s="1">
+      <c r="H15" s="4">
         <v>387</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" s="4" customFormat="1">
+      <c r="A16" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" s="4">
+        <v>-431</v>
+      </c>
+      <c r="C16" s="4">
+        <v>-2062</v>
+      </c>
+      <c r="D16" s="4">
+        <v>-1146</v>
+      </c>
+      <c r="E16" s="4">
+        <v>-3264</v>
+      </c>
+      <c r="F16" s="4">
+        <v>-1895</v>
+      </c>
+      <c r="G16" s="4">
+        <v>6</v>
+      </c>
+      <c r="H16" s="4">
+        <v>43</v>
+      </c>
+      <c r="I16" s="4">
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B17" s="1">
-        <v>4335</v>
+        <v>2254</v>
       </c>
       <c r="C17" s="1">
-        <v>1641</v>
+        <v>2393</v>
       </c>
       <c r="D17" s="1">
-        <v>854</v>
+        <v>2811</v>
       </c>
       <c r="E17" s="1">
-        <v>1320</v>
-      </c>
-      <c r="F17" s="1">
-        <v>3162</v>
-      </c>
-      <c r="G17" s="1">
-        <v>2490</v>
-      </c>
-      <c r="H17" s="1">
-        <v>341</v>
-      </c>
-      <c r="I17" s="1">
-        <v>337</v>
-      </c>
-      <c r="J17" s="1">
-        <v>-33</v>
+        <v>3548</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="B18" s="1">
-        <v>6493</v>
+        <v>5539</v>
       </c>
       <c r="C18" s="1">
-        <v>3041</v>
+        <v>3787</v>
       </c>
       <c r="D18" s="1">
-        <v>1667</v>
+        <v>-902</v>
       </c>
       <c r="E18" s="1">
-        <v>3565</v>
+        <v>2535</v>
       </c>
       <c r="F18" s="1">
-        <v>3521</v>
+        <v>940</v>
       </c>
       <c r="G18" s="1">
-        <v>1071</v>
+        <v>125</v>
       </c>
       <c r="H18" s="1">
-        <v>493</v>
+        <v>387</v>
       </c>
       <c r="I18" s="1">
-        <v>34</v>
+        <v>-108</v>
       </c>
       <c r="J18" s="1">
-        <v>12</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B19" s="1">
         <v>285</v>
       </c>
       <c r="C19" s="1">
-        <v>113</v>
+        <v>279</v>
       </c>
       <c r="D19" s="1">
-        <v>98</v>
+        <v>268</v>
       </c>
       <c r="E19" s="1">
-        <v>88</v>
+        <v>167</v>
       </c>
       <c r="F19" s="1">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="G19" s="1">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="H19" s="1">
-        <v>36</v>
+        <v>74</v>
+      </c>
+      <c r="I19" s="1">
+        <v>70</v>
+      </c>
+      <c r="J19" s="1">
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" s="1">
-        <v>-11</v>
-      </c>
-      <c r="C20" s="1">
-        <v>343</v>
-      </c>
-      <c r="D20" s="1">
-        <v>-472</v>
-      </c>
-      <c r="E20" s="1">
-        <v>-1197</v>
-      </c>
-      <c r="F20" s="1">
-        <v>-920</v>
-      </c>
-      <c r="G20" s="1">
-        <v>-231</v>
+        <v>26</v>
       </c>
       <c r="H20" s="1">
-        <v>-176</v>
+        <v>-403</v>
       </c>
       <c r="I20" s="1">
-        <v>-70</v>
+        <v>-41</v>
       </c>
       <c r="J20" s="1">
-        <v>-167</v>
+        <v>-110</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B21" s="1">
-        <v>17</v>
+        <v>285</v>
       </c>
       <c r="C21" s="1">
-        <v>24</v>
+        <v>113</v>
+      </c>
+      <c r="D21" s="1">
+        <v>98</v>
+      </c>
+      <c r="E21" s="1">
+        <v>88</v>
+      </c>
+      <c r="F21" s="1">
+        <v>56</v>
+      </c>
+      <c r="G21" s="1">
+        <v>42</v>
+      </c>
+      <c r="H21" s="1">
+        <v>36</v>
+      </c>
+      <c r="I21" s="1">
+        <v>0</v>
+      </c>
+      <c r="J21" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>14</v>
+      </c>
+      <c r="B22" s="1">
+        <v>17</v>
+      </c>
+      <c r="C22" s="1">
+        <v>24</v>
       </c>
       <c r="D22" s="1">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E22" s="1">
-        <v>16</v>
-      </c>
-      <c r="F22" s="1">
-        <v>34</v>
-      </c>
-      <c r="G22" s="1">
-        <v>33</v>
-      </c>
-      <c r="H22" s="1">
-        <v>42</v>
-      </c>
-      <c r="I22" s="1">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="1">
+        <v>11</v>
+      </c>
+      <c r="E23" s="1">
+        <v>16</v>
+      </c>
+      <c r="F23" s="1">
+        <v>34</v>
+      </c>
+      <c r="G23" s="1">
+        <v>33</v>
+      </c>
+      <c r="H23" s="1">
+        <v>42</v>
+      </c>
+      <c r="I23" s="1">
         <v>27</v>
       </c>
-      <c r="D23" s="1">
-        <v>-7</v>
-      </c>
-      <c r="E23" s="1">
-        <v>-13</v>
-      </c>
-      <c r="F23" s="1">
-        <v>8</v>
-      </c>
-      <c r="G23" s="1">
-        <v>10</v>
-      </c>
-      <c r="H23" s="1">
-        <v>14</v>
-      </c>
-      <c r="I23" s="1">
-        <v>-28</v>
+      <c r="J23" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>29</v>
+        <v>36</v>
+      </c>
+      <c r="D24" s="1">
+        <v>-7</v>
+      </c>
+      <c r="E24" s="1">
+        <v>-13</v>
+      </c>
+      <c r="F24" s="1">
+        <v>8</v>
+      </c>
+      <c r="G24" s="1">
+        <v>10</v>
       </c>
       <c r="H24" s="1">
-        <v>-70</v>
+        <v>14</v>
       </c>
       <c r="I24" s="1">
-        <v>0</v>
-      </c>
-      <c r="J24" s="1">
-        <v>70</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>30</v>
-      </c>
-      <c r="B25" s="1">
-        <v>-5470</v>
-      </c>
-      <c r="C25" s="1">
-        <v>-1493</v>
-      </c>
-      <c r="D25" s="1">
-        <v>-3722</v>
-      </c>
-      <c r="E25" s="1">
-        <v>-2667</v>
-      </c>
-      <c r="F25" s="1">
-        <v>-2056</v>
-      </c>
-      <c r="G25" s="1">
-        <v>-850</v>
+        <v>24</v>
       </c>
       <c r="H25" s="1">
-        <v>-284</v>
+        <v>-70</v>
       </c>
       <c r="I25" s="1">
-        <v>-123</v>
+        <v>0</v>
+      </c>
+      <c r="J25" s="1">
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="B26" s="1">
-        <v>1638</v>
+        <v>-5470</v>
       </c>
       <c r="C26" s="1">
-        <v>1407</v>
+        <v>-1493</v>
       </c>
       <c r="D26" s="1">
-        <v>1384</v>
+        <v>-3722</v>
       </c>
       <c r="E26" s="1">
-        <v>1081</v>
+        <v>-2667</v>
       </c>
       <c r="F26" s="1">
-        <v>379</v>
+        <v>-2056</v>
       </c>
       <c r="G26" s="1">
-        <v>274</v>
+        <v>-850</v>
       </c>
       <c r="H26" s="1">
-        <v>197</v>
+        <v>-284</v>
       </c>
       <c r="I26" s="1">
-        <v>137</v>
-      </c>
-      <c r="J26" s="1">
-        <v>97</v>
+        <v>-123</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B27" s="1">
         <v>860</v>
       </c>
+      <c r="C27" s="1">
+        <v>0</v>
+      </c>
+      <c r="D27" s="1">
+        <v>0</v>
+      </c>
       <c r="E27" s="1">
         <v>48514</v>
+      </c>
+      <c r="F27" s="1">
+        <v>0</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2665,57 +2737,57 @@
         <v>9</v>
       </c>
       <c r="B4" s="1">
-        <v>9882</v>
+        <v>14265</v>
       </c>
       <c r="C4" s="1">
-        <v>12556</v>
+        <v>8249</v>
       </c>
       <c r="D4" s="1">
-        <v>8578</v>
+        <v>7079</v>
       </c>
       <c r="E4" s="1">
-        <v>9595</v>
+        <v>11144</v>
       </c>
       <c r="F4" s="1">
-        <v>5747</v>
+        <v>4827</v>
       </c>
       <c r="G4" s="1">
-        <v>5581</v>
+        <v>5865</v>
       </c>
       <c r="H4" s="1">
-        <v>4128</v>
+        <v>4194</v>
       </c>
       <c r="I4" s="1">
-        <v>3824</v>
+        <v>3019</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1">
-        <v>3839</v>
+        <v>23151</v>
       </c>
       <c r="C5" s="1">
-        <v>3478</v>
+        <v>13813</v>
       </c>
       <c r="D5" s="1">
-        <v>3402</v>
+        <v>17955</v>
       </c>
       <c r="E5" s="1">
-        <v>4133</v>
+        <v>17194</v>
       </c>
       <c r="F5" s="1">
-        <v>9457</v>
+        <v>2103</v>
       </c>
       <c r="G5" s="1">
-        <v>6782</v>
+        <v>2292</v>
       </c>
       <c r="H5" s="1">
-        <v>7659</v>
+        <v>1082</v>
       </c>
       <c r="I5" s="1">
-        <v>6722</v>
+        <v>2788</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2723,193 +2795,202 @@
         <v>12</v>
       </c>
       <c r="B6" s="1">
-        <v>113</v>
+        <v>3839</v>
       </c>
       <c r="C6" s="1">
-        <v>-711</v>
+        <v>3478</v>
       </c>
       <c r="D6" s="1">
-        <v>-215</v>
+        <v>3402</v>
       </c>
       <c r="E6" s="1">
-        <v>-562</v>
+        <v>4133</v>
       </c>
       <c r="F6" s="1">
-        <v>-880</v>
+        <v>9457</v>
       </c>
       <c r="G6" s="1">
-        <v>-751</v>
+        <v>6782</v>
       </c>
       <c r="H6" s="1">
-        <v>-1280</v>
+        <v>7659</v>
       </c>
       <c r="I6" s="1">
-        <v>-974</v>
+        <v>6722</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1">
-        <v>14265</v>
+        <v>11618</v>
       </c>
       <c r="C7" s="1">
-        <v>8249</v>
+        <v>12198</v>
       </c>
       <c r="D7" s="1">
-        <v>7079</v>
+        <v>11127</v>
       </c>
       <c r="E7" s="1">
-        <v>11144</v>
+        <v>13224</v>
       </c>
       <c r="F7" s="1">
-        <v>4827</v>
+        <v>10776</v>
       </c>
       <c r="G7" s="1">
-        <v>5865</v>
+        <v>8427</v>
       </c>
       <c r="H7" s="1">
-        <v>4194</v>
+        <v>8744</v>
       </c>
       <c r="I7" s="1">
-        <v>3019</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" t="s">
+        <v>7253</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" s="4" customFormat="1">
+      <c r="A8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="1">
-        <v>65185</v>
-      </c>
-      <c r="C8" s="1">
-        <v>50949</v>
-      </c>
-      <c r="D8" s="1">
-        <v>36649</v>
-      </c>
-      <c r="E8" s="1">
-        <v>31580</v>
-      </c>
-      <c r="F8" s="1">
-        <v>28006</v>
-      </c>
-      <c r="G8" s="1">
-        <v>25556</v>
-      </c>
-      <c r="H8" s="1">
-        <v>25261</v>
-      </c>
-      <c r="I8" s="1">
-        <v>25365</v>
+      <c r="B8" s="4">
+        <v>63688</v>
+      </c>
+      <c r="C8" s="4">
+        <v>47324</v>
+      </c>
+      <c r="D8" s="4">
+        <v>43269</v>
+      </c>
+      <c r="E8" s="4">
+        <v>50407</v>
+      </c>
+      <c r="F8" s="4">
+        <v>57718</v>
+      </c>
+      <c r="G8" s="4">
+        <v>47249</v>
+      </c>
+      <c r="H8" s="4">
+        <v>31239</v>
+      </c>
+      <c r="I8" s="4">
+        <v>28787</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>58</v>
+        <v>18</v>
+      </c>
+      <c r="B9" s="1">
+        <v>23912</v>
+      </c>
+      <c r="C9" s="1">
+        <v>24693</v>
+      </c>
+      <c r="D9" s="1">
+        <v>27591</v>
       </c>
       <c r="E9" s="1">
-        <v>202</v>
+        <v>27591</v>
       </c>
       <c r="F9" s="1">
-        <v>2667</v>
+        <v>26963</v>
       </c>
       <c r="G9" s="1">
-        <v>3843</v>
+        <v>26971</v>
       </c>
       <c r="H9" s="1">
-        <v>2044</v>
+        <v>26276</v>
       </c>
       <c r="I9" s="1">
-        <v>1665</v>
+        <v>24513</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="B10" s="1">
-        <v>23912</v>
+        <v>2772</v>
       </c>
       <c r="C10" s="1">
-        <v>24693</v>
+        <v>3691</v>
       </c>
       <c r="D10" s="1">
-        <v>27591</v>
+        <v>4589</v>
       </c>
       <c r="E10" s="1">
-        <v>27591</v>
+        <v>6018</v>
       </c>
       <c r="F10" s="1">
-        <v>26963</v>
+        <v>7270</v>
       </c>
       <c r="G10" s="1">
-        <v>26971</v>
+        <v>9026</v>
       </c>
       <c r="H10" s="1">
-        <v>26276</v>
+        <v>10827</v>
       </c>
       <c r="I10" s="1">
-        <v>24513</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" t="s">
-        <v>66</v>
-      </c>
-      <c r="B11" s="1">
-        <v>2772</v>
-      </c>
-      <c r="C11" s="1">
-        <v>3691</v>
-      </c>
-      <c r="D11" s="1">
-        <v>4589</v>
-      </c>
-      <c r="E11" s="1">
-        <v>6018</v>
-      </c>
-      <c r="F11" s="1">
-        <v>7270</v>
-      </c>
-      <c r="G11" s="1">
-        <v>9026</v>
-      </c>
-      <c r="H11" s="1">
-        <v>10827</v>
-      </c>
-      <c r="I11" s="1">
         <v>11836</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" s="4" customFormat="1">
+      <c r="A11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="4">
+        <v>211429</v>
+      </c>
+      <c r="C11" s="4">
+        <v>196485</v>
+      </c>
+      <c r="D11" s="4">
+        <v>191572</v>
+      </c>
+      <c r="E11" s="4">
+        <v>182103</v>
+      </c>
+      <c r="F11" s="4">
+        <v>168406</v>
+      </c>
+      <c r="G11" s="4">
+        <v>153091</v>
+      </c>
+      <c r="H11" s="4">
+        <v>136524</v>
+      </c>
+      <c r="I11" s="4">
+        <v>127963</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1">
-        <v>11618</v>
+        <v>9882</v>
       </c>
       <c r="C12" s="1">
-        <v>12198</v>
+        <v>12556</v>
       </c>
       <c r="D12" s="1">
-        <v>11127</v>
+        <v>8578</v>
       </c>
       <c r="E12" s="1">
-        <v>13224</v>
+        <v>9595</v>
       </c>
       <c r="F12" s="1">
-        <v>10776</v>
+        <v>5747</v>
       </c>
       <c r="G12" s="1">
-        <v>8427</v>
+        <v>5581</v>
       </c>
       <c r="H12" s="1">
-        <v>8744</v>
+        <v>4128</v>
       </c>
       <c r="I12" s="1">
-        <v>7253</v>
+        <v>3824</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -2917,202 +2998,187 @@
         <v>24</v>
       </c>
       <c r="B13" s="1">
-        <v>9408</v>
+        <v>2499</v>
       </c>
       <c r="C13" s="1">
-        <v>9505</v>
+        <v>3729</v>
       </c>
       <c r="D13" s="1">
-        <v>6576</v>
+        <v>2288</v>
       </c>
       <c r="E13" s="1">
-        <v>4980</v>
+        <v>4367</v>
       </c>
       <c r="F13" s="1">
-        <v>4886</v>
+        <v>4591</v>
       </c>
       <c r="G13" s="1">
-        <v>3614</v>
+        <v>2504</v>
       </c>
       <c r="H13" s="1">
-        <v>2916</v>
+        <v>3693</v>
       </c>
       <c r="I13" s="1">
-        <v>2646</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" t="s">
-        <v>67</v>
-      </c>
-      <c r="B14" s="1">
-        <v>0</v>
-      </c>
-      <c r="C14" s="1">
-        <v>0</v>
-      </c>
-      <c r="D14" s="1">
-        <v>0</v>
-      </c>
-      <c r="E14" s="1">
-        <v>0</v>
-      </c>
-      <c r="F14" s="1">
-        <v>0</v>
-      </c>
-      <c r="G14" s="1">
-        <v>0</v>
-      </c>
-      <c r="H14" s="1">
-        <v>0</v>
-      </c>
-      <c r="I14" s="1">
-        <v>0</v>
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" s="4" customFormat="1">
+      <c r="A14" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="4">
+        <v>31575</v>
+      </c>
+      <c r="C14" s="4">
+        <v>35666</v>
+      </c>
+      <c r="D14" s="4">
+        <v>28053</v>
+      </c>
+      <c r="E14" s="4">
+        <v>32155</v>
+      </c>
+      <c r="F14" s="4">
+        <v>27462</v>
+      </c>
+      <c r="G14" s="4">
+        <v>24754</v>
+      </c>
+      <c r="H14" s="4">
+        <v>22310</v>
+      </c>
+      <c r="I14" s="4">
+        <v>16626</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B15" s="1">
-        <v>48983</v>
+        <v>9408</v>
       </c>
       <c r="C15" s="1">
-        <v>49032</v>
+        <v>9505</v>
       </c>
       <c r="D15" s="1">
-        <v>69156</v>
+        <v>6576</v>
       </c>
       <c r="E15" s="1">
-        <v>70405</v>
+        <v>4980</v>
       </c>
       <c r="F15" s="1">
-        <v>68265</v>
+        <v>4886</v>
       </c>
       <c r="G15" s="1">
-        <v>56233</v>
+        <v>3614</v>
       </c>
       <c r="H15" s="1">
-        <v>53523</v>
+        <v>2916</v>
       </c>
       <c r="I15" s="1">
-        <v>50172</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="1">
-        <v>2499</v>
-      </c>
-      <c r="C16" s="1">
-        <v>3729</v>
-      </c>
-      <c r="D16" s="1">
-        <v>2288</v>
-      </c>
-      <c r="E16" s="1">
-        <v>4367</v>
-      </c>
-      <c r="F16" s="1">
-        <v>4591</v>
-      </c>
-      <c r="G16" s="1">
-        <v>2504</v>
-      </c>
-      <c r="H16" s="1">
-        <v>3693</v>
-      </c>
-      <c r="I16" s="1">
-        <v>1261</v>
+        <v>2646</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" s="4" customFormat="1">
+      <c r="A16" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="G16" s="4">
+        <v>153091</v>
+      </c>
+      <c r="H16" s="4">
+        <v>136524</v>
+      </c>
+      <c r="I16" s="4">
+        <v>127963</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="B17" s="1">
-        <v>23151</v>
+        <v>0</v>
       </c>
       <c r="C17" s="1">
-        <v>13813</v>
+        <v>0</v>
       </c>
       <c r="D17" s="1">
-        <v>17955</v>
+        <v>0</v>
       </c>
       <c r="E17" s="1">
-        <v>17194</v>
+        <v>0</v>
       </c>
       <c r="F17" s="1">
-        <v>2103</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>2292</v>
+        <v>0</v>
       </c>
       <c r="H17" s="1">
-        <v>1082</v>
+        <v>0</v>
       </c>
       <c r="I17" s="1">
-        <v>2788</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B18" s="1">
-        <v>126360</v>
+        <v>65185</v>
       </c>
       <c r="C18" s="1">
-        <v>105032</v>
+        <v>50949</v>
       </c>
       <c r="D18" s="1">
-        <v>109965</v>
+        <v>36649</v>
       </c>
       <c r="E18" s="1">
-        <v>103286</v>
+        <v>31580</v>
       </c>
       <c r="F18" s="1">
-        <v>95391</v>
+        <v>28006</v>
       </c>
       <c r="G18" s="1">
-        <v>81038</v>
+        <v>25556</v>
       </c>
       <c r="H18" s="1">
-        <v>77504</v>
+        <v>25261</v>
       </c>
       <c r="I18" s="1">
-        <v>74563</v>
+        <v>25365</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B19" s="1">
-        <v>211429</v>
+        <v>113</v>
       </c>
       <c r="C19" s="1">
-        <v>196485</v>
+        <v>-711</v>
       </c>
       <c r="D19" s="1">
-        <v>191572</v>
+        <v>-215</v>
       </c>
       <c r="E19" s="1">
-        <v>182103</v>
+        <v>-562</v>
       </c>
       <c r="F19" s="1">
-        <v>168406</v>
+        <v>-880</v>
       </c>
       <c r="G19" s="1">
-        <v>153091</v>
+        <v>-751</v>
       </c>
       <c r="H19" s="1">
-        <v>136524</v>
+        <v>-1280</v>
       </c>
       <c r="I19" s="1">
-        <v>127963</v>
+        <v>-974</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -3120,94 +3186,100 @@
         <v>33</v>
       </c>
       <c r="B20" s="1">
-        <v>63688</v>
+        <v>48983</v>
       </c>
       <c r="C20" s="1">
-        <v>47324</v>
+        <v>49032</v>
       </c>
       <c r="D20" s="1">
-        <v>43269</v>
+        <v>69156</v>
       </c>
       <c r="E20" s="1">
-        <v>50407</v>
+        <v>70405</v>
       </c>
       <c r="F20" s="1">
-        <v>57718</v>
+        <v>68265</v>
       </c>
       <c r="G20" s="1">
-        <v>47249</v>
+        <v>56233</v>
       </c>
       <c r="H20" s="1">
-        <v>31239</v>
+        <v>53523</v>
       </c>
       <c r="I20" s="1">
-        <v>28787</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" t="s">
+        <v>50172</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" s="4" customFormat="1">
+      <c r="A21" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B21" s="1">
-        <v>31575</v>
-      </c>
-      <c r="C21" s="1">
-        <v>35666</v>
-      </c>
-      <c r="D21" s="1">
-        <v>28053</v>
-      </c>
-      <c r="E21" s="1">
-        <v>32155</v>
-      </c>
-      <c r="F21" s="1">
-        <v>27462</v>
-      </c>
-      <c r="G21" s="1">
-        <v>24754</v>
-      </c>
-      <c r="H21" s="1">
-        <v>22310</v>
-      </c>
-      <c r="I21" s="1">
-        <v>16626</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="A22" t="s">
-        <v>68</v>
-      </c>
-      <c r="G22" s="1">
+      <c r="B21" s="4">
+        <v>126360</v>
+      </c>
+      <c r="C21" s="4">
+        <v>105032</v>
+      </c>
+      <c r="D21" s="4">
+        <v>109965</v>
+      </c>
+      <c r="E21" s="4">
+        <v>103286</v>
+      </c>
+      <c r="F21" s="4">
+        <v>95391</v>
+      </c>
+      <c r="G21" s="4">
+        <v>81038</v>
+      </c>
+      <c r="H21" s="4">
+        <v>77504</v>
+      </c>
+      <c r="I21" s="4">
+        <v>74563</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" s="4" customFormat="1">
+      <c r="A22" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="4">
+        <v>211429</v>
+      </c>
+      <c r="C22" s="4">
+        <v>196485</v>
+      </c>
+      <c r="D22" s="4">
+        <v>191572</v>
+      </c>
+      <c r="E22" s="4">
+        <v>182103</v>
+      </c>
+      <c r="F22" s="4">
+        <v>168406</v>
+      </c>
+      <c r="G22" s="4">
         <v>153091</v>
-      </c>
-      <c r="H22" s="1">
-        <v>136524</v>
-      </c>
-      <c r="I22" s="1">
-        <v>127963</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>35</v>
-      </c>
-      <c r="B23" s="1">
-        <v>211429</v>
-      </c>
-      <c r="C23" s="1">
-        <v>196485</v>
-      </c>
-      <c r="D23" s="1">
-        <v>191572</v>
+        <v>59</v>
       </c>
       <c r="E23" s="1">
-        <v>182103</v>
+        <v>202</v>
       </c>
       <c r="F23" s="1">
-        <v>168406</v>
+        <v>2667</v>
       </c>
       <c r="G23" s="1">
-        <v>153091</v>
+        <v>3843</v>
+      </c>
+      <c r="H23" s="1">
+        <v>2044</v>
+      </c>
+      <c r="I23" s="1">
+        <v>1665</v>
       </c>
     </row>
   </sheetData>
@@ -3218,7 +3290,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="42.7109375" customWidth="1"/>
@@ -3227,7 +3299,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="24" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="8" customHeight="1"/>
@@ -3267,14 +3339,32 @@
       <c r="A4" t="s">
         <v>39</v>
       </c>
+      <c r="B4" s="1">
+        <v>52853</v>
+      </c>
+      <c r="C4" s="1">
+        <v>53101</v>
+      </c>
+      <c r="D4" s="1">
+        <v>54228</v>
+      </c>
+      <c r="E4" s="1">
+        <v>63054</v>
+      </c>
+      <c r="F4" s="1">
+        <v>79024</v>
+      </c>
+      <c r="G4" s="1">
+        <v>77867</v>
+      </c>
       <c r="H4" s="1">
-        <v>200</v>
+        <v>71965</v>
       </c>
       <c r="I4" s="1">
-        <v>200</v>
+        <v>70848</v>
       </c>
       <c r="J4" s="1">
-        <v>177</v>
+        <v>62761</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3282,95 +3372,77 @@
         <v>40</v>
       </c>
       <c r="B5" s="1">
-        <v>-0.06</v>
+        <v>34478</v>
       </c>
       <c r="C5" s="1">
-        <v>-4.38</v>
+        <v>35756</v>
       </c>
       <c r="D5" s="1">
-        <v>0.4</v>
+        <v>32517</v>
       </c>
       <c r="E5" s="1">
-        <v>1.95</v>
+        <v>36188</v>
       </c>
       <c r="F5" s="1">
-        <v>4.89</v>
+        <v>35209</v>
       </c>
       <c r="G5" s="1">
-        <v>4.98</v>
+        <v>34255</v>
       </c>
       <c r="H5" s="1">
-        <v>4.77</v>
+        <v>29825</v>
       </c>
       <c r="I5" s="1">
-        <v>4.57</v>
+        <v>27111</v>
       </c>
       <c r="J5" s="1">
-        <v>2.04</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="1">
-        <v>34478</v>
-      </c>
-      <c r="C6" s="1">
-        <v>35756</v>
-      </c>
-      <c r="D6" s="1">
-        <v>32517</v>
-      </c>
-      <c r="E6" s="1">
-        <v>36188</v>
-      </c>
-      <c r="F6" s="1">
-        <v>35209</v>
-      </c>
-      <c r="G6" s="1">
-        <v>34255</v>
-      </c>
-      <c r="H6" s="1">
-        <v>29825</v>
-      </c>
-      <c r="I6" s="1">
-        <v>27111</v>
-      </c>
-      <c r="J6" s="1">
         <v>23663</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="4" customFormat="1">
+      <c r="A6" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="4">
+        <v>18375</v>
+      </c>
+      <c r="C6" s="4">
+        <v>17345</v>
+      </c>
+      <c r="D6" s="4">
+        <v>21711</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B7" s="1">
-        <v>-0.06</v>
+        <v>13774</v>
       </c>
       <c r="C7" s="1">
-        <v>-4.38</v>
+        <v>16546</v>
       </c>
       <c r="D7" s="1">
-        <v>0.4</v>
+        <v>16046</v>
       </c>
       <c r="E7" s="1">
-        <v>1.94</v>
+        <v>17528</v>
       </c>
       <c r="F7" s="1">
-        <v>4.86</v>
+        <v>15190</v>
       </c>
       <c r="G7" s="1">
-        <v>4.94</v>
+        <v>13556</v>
       </c>
       <c r="H7" s="1">
-        <v>4.71</v>
+        <v>13362</v>
       </c>
       <c r="I7" s="1">
-        <v>4.48</v>
+        <v>13543</v>
       </c>
       <c r="J7" s="1">
-        <v>1.99</v>
+        <v>13035</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -3378,217 +3450,231 @@
         <v>44</v>
       </c>
       <c r="B8" s="1">
-        <v>18375</v>
+        <v>4624</v>
       </c>
       <c r="C8" s="1">
-        <v>17345</v>
+        <v>5507</v>
       </c>
       <c r="D8" s="1">
-        <v>21711</v>
+        <v>5634</v>
+      </c>
+      <c r="E8" s="1">
+        <v>7002</v>
+      </c>
+      <c r="F8" s="1">
+        <v>6543</v>
+      </c>
+      <c r="G8" s="1">
+        <v>6180</v>
+      </c>
+      <c r="H8" s="1">
+        <v>6150</v>
+      </c>
+      <c r="I8" s="1">
+        <v>6950</v>
+      </c>
+      <c r="J8" s="1">
+        <v>7452</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" s="1">
-        <v>762</v>
-      </c>
-      <c r="E9" s="1">
-        <v>7768</v>
-      </c>
-      <c r="F9" s="1">
-        <v>21703</v>
-      </c>
-      <c r="G9" s="1">
-        <v>25078</v>
+        <v>45</v>
       </c>
       <c r="H9" s="1">
-        <v>24058</v>
+        <v>200</v>
       </c>
       <c r="I9" s="1">
-        <v>23317</v>
+        <v>200</v>
       </c>
       <c r="J9" s="1">
-        <v>20352</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" t="s">
-        <v>49</v>
-      </c>
-      <c r="B10" s="1">
-        <v>4624</v>
-      </c>
-      <c r="C10" s="1">
-        <v>5507</v>
-      </c>
-      <c r="D10" s="1">
-        <v>5634</v>
-      </c>
-      <c r="E10" s="1">
-        <v>7002</v>
-      </c>
-      <c r="F10" s="1">
-        <v>6543</v>
-      </c>
-      <c r="G10" s="1">
-        <v>6180</v>
-      </c>
-      <c r="H10" s="1">
-        <v>6150</v>
-      </c>
-      <c r="I10" s="1">
-        <v>6950</v>
-      </c>
-      <c r="J10" s="1">
-        <v>7452</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" s="1">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" s="4" customFormat="1">
+      <c r="A10" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="4">
+        <v>20589</v>
+      </c>
+      <c r="C10" s="4">
+        <v>29023</v>
+      </c>
+      <c r="D10" s="4">
+        <v>21618</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" s="4" customFormat="1">
+      <c r="A11" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="4">
+        <v>-2214</v>
+      </c>
+      <c r="C11" s="4">
+        <v>-11678</v>
+      </c>
+      <c r="D11" s="4">
+        <v>93</v>
+      </c>
+      <c r="E11" s="4">
+        <v>2334</v>
+      </c>
+      <c r="F11" s="4">
+        <v>19456</v>
+      </c>
+      <c r="G11" s="4">
+        <v>23678</v>
+      </c>
+      <c r="H11" s="4">
+        <v>22035</v>
+      </c>
+      <c r="I11" s="4">
+        <v>23316</v>
+      </c>
+      <c r="J11" s="4">
+        <v>18050</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" s="4" customFormat="1">
+      <c r="A12" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="4">
         <v>26</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C12" s="4">
         <v>-19233</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D12" s="4">
         <v>1675</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E12" s="4">
         <v>8017</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F12" s="4">
         <v>19868</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G12" s="4">
         <v>20899</v>
       </c>
-      <c r="H11" s="1">
+      <c r="H12" s="4">
         <v>21048</v>
       </c>
-      <c r="I11" s="1">
+      <c r="I12" s="4">
         <v>21053</v>
       </c>
-      <c r="J11" s="1">
+      <c r="J12" s="4">
         <v>9601</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" t="s">
-        <v>51</v>
-      </c>
-      <c r="B12" s="1">
-        <v>-2214</v>
-      </c>
-      <c r="C12" s="1">
-        <v>-11678</v>
-      </c>
-      <c r="D12" s="1">
-        <v>93</v>
-      </c>
-      <c r="E12" s="1">
-        <v>2334</v>
-      </c>
-      <c r="F12" s="1">
-        <v>19456</v>
-      </c>
-      <c r="G12" s="1">
-        <v>23678</v>
-      </c>
-      <c r="H12" s="1">
-        <v>22035</v>
-      </c>
-      <c r="I12" s="1">
-        <v>23316</v>
-      </c>
-      <c r="J12" s="1">
-        <v>18050</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B13" s="1">
-        <v>13774</v>
+        <v>-0.06</v>
       </c>
       <c r="C13" s="1">
-        <v>16546</v>
+        <v>-4.38</v>
       </c>
       <c r="D13" s="1">
-        <v>16046</v>
+        <v>0.4</v>
       </c>
       <c r="E13" s="1">
-        <v>17528</v>
+        <v>1.95</v>
       </c>
       <c r="F13" s="1">
-        <v>15190</v>
+        <v>4.89</v>
       </c>
       <c r="G13" s="1">
-        <v>13556</v>
+        <v>4.98</v>
       </c>
       <c r="H13" s="1">
-        <v>13362</v>
+        <v>4.77</v>
       </c>
       <c r="I13" s="1">
-        <v>13543</v>
+        <v>4.57</v>
       </c>
       <c r="J13" s="1">
-        <v>13035</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B14" s="1">
-        <v>52853</v>
+        <v>-0.06</v>
       </c>
       <c r="C14" s="1">
-        <v>53101</v>
+        <v>-4.38</v>
       </c>
       <c r="D14" s="1">
-        <v>54228</v>
+        <v>0.4</v>
       </c>
       <c r="E14" s="1">
-        <v>63054</v>
+        <v>1.94</v>
       </c>
       <c r="F14" s="1">
-        <v>79024</v>
+        <v>4.86</v>
       </c>
       <c r="G14" s="1">
-        <v>77867</v>
+        <v>4.94</v>
       </c>
       <c r="H14" s="1">
-        <v>71965</v>
+        <v>4.71</v>
       </c>
       <c r="I14" s="1">
-        <v>70848</v>
+        <v>4.48</v>
       </c>
       <c r="J14" s="1">
-        <v>62761</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>55</v>
-      </c>
-      <c r="B15" s="1">
-        <v>20589</v>
-      </c>
-      <c r="C15" s="1">
-        <v>29023</v>
+        <v>70</v>
       </c>
       <c r="D15" s="1">
-        <v>21618</v>
+        <v>762</v>
+      </c>
+      <c r="E15" s="1">
+        <v>7768</v>
+      </c>
+      <c r="F15" s="1">
+        <v>21703</v>
+      </c>
+      <c r="G15" s="1">
+        <v>25078</v>
+      </c>
+      <c r="H15" s="1">
+        <v>24058</v>
+      </c>
+      <c r="I15" s="1">
+        <v>23317</v>
+      </c>
+      <c r="J15" s="1">
+        <v>20352</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E16" s="1">
+        <v>3</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J15"/>
+  <autoFilter ref="A3:J16"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3604,7 +3690,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="24" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="8" customHeight="1"/>
@@ -3640,399 +3726,402 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="1">
-        <v>297</v>
-      </c>
-      <c r="C4" s="1">
-        <v>634</v>
-      </c>
-      <c r="D4" s="1">
-        <v>-801</v>
-      </c>
-      <c r="E4" s="1">
-        <v>-29</v>
-      </c>
-      <c r="F4" s="1">
-        <v>1190</v>
-      </c>
-      <c r="G4" s="1">
-        <v>412</v>
-      </c>
-      <c r="H4" s="1">
-        <v>696</v>
-      </c>
-      <c r="I4" s="1">
-        <v>211</v>
-      </c>
-      <c r="J4" s="1">
-        <v>191</v>
+    <row r="4" spans="1:10" s="4" customFormat="1">
+      <c r="A4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>26</v>
+      </c>
+      <c r="C4" s="4">
+        <v>-19233</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1675</v>
+      </c>
+      <c r="E4" s="4">
+        <v>8017</v>
+      </c>
+      <c r="F4" s="4">
+        <v>19868</v>
+      </c>
+      <c r="G4" s="4">
+        <v>20899</v>
+      </c>
+      <c r="H4" s="4">
+        <v>21048</v>
+      </c>
+      <c r="I4" s="4">
+        <v>21053</v>
+      </c>
+      <c r="J4" s="4">
+        <v>9601</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="B5" s="1">
-        <v>-449</v>
+        <v>10757</v>
       </c>
       <c r="C5" s="1">
-        <v>-75</v>
+        <v>9951</v>
       </c>
       <c r="D5" s="1">
-        <v>731</v>
+        <v>7847</v>
       </c>
       <c r="E5" s="1">
-        <v>5327</v>
+        <v>11128</v>
       </c>
       <c r="F5" s="1">
-        <v>-2674</v>
+        <v>9953</v>
       </c>
       <c r="G5" s="1">
-        <v>883</v>
+        <v>10482</v>
       </c>
       <c r="H5" s="1">
-        <v>-935</v>
+        <v>9204</v>
       </c>
       <c r="I5" s="1">
-        <v>-1714</v>
+        <v>7520</v>
       </c>
       <c r="J5" s="1">
-        <v>-781</v>
+        <v>6752</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="B6" s="1">
-        <v>6463</v>
+        <v>2434</v>
       </c>
       <c r="C6" s="1">
-        <v>1170</v>
+        <v>3410</v>
       </c>
       <c r="D6" s="1">
-        <v>-4065</v>
+        <v>3229</v>
       </c>
       <c r="E6" s="1">
-        <v>6317</v>
+        <v>3128</v>
       </c>
       <c r="F6" s="1">
-        <v>-1038</v>
+        <v>2036</v>
       </c>
       <c r="G6" s="1">
-        <v>1671</v>
+        <v>1854</v>
       </c>
       <c r="H6" s="1">
-        <v>1175</v>
+        <v>1705</v>
       </c>
       <c r="I6" s="1">
-        <v>-414</v>
+        <v>1546</v>
       </c>
       <c r="J6" s="1">
-        <v>-2127</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="B7" s="1">
-        <v>8249</v>
+        <v>-449</v>
       </c>
       <c r="C7" s="1">
-        <v>7079</v>
+        <v>-75</v>
       </c>
       <c r="D7" s="1">
-        <v>11144</v>
+        <v>731</v>
       </c>
       <c r="E7" s="1">
-        <v>4827</v>
+        <v>5327</v>
       </c>
       <c r="F7" s="1">
-        <v>5865</v>
+        <v>-2674</v>
       </c>
       <c r="G7" s="1">
-        <v>4194</v>
+        <v>883</v>
       </c>
       <c r="H7" s="1">
-        <v>3019</v>
+        <v>-935</v>
       </c>
       <c r="I7" s="1">
-        <v>3433</v>
+        <v>-1714</v>
       </c>
       <c r="J7" s="1">
-        <v>5560</v>
+        <v>-781</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B8" s="1">
-        <v>771</v>
+        <v>-138</v>
       </c>
       <c r="C8" s="1">
-        <v>987</v>
+        <v>-1105</v>
       </c>
       <c r="D8" s="1">
-        <v>1042</v>
+        <v>2097</v>
       </c>
       <c r="E8" s="1">
-        <v>977</v>
+        <v>-2436</v>
       </c>
       <c r="F8" s="1">
-        <v>1020</v>
+        <v>-2339</v>
       </c>
       <c r="G8" s="1">
-        <v>897</v>
+        <v>-687</v>
       </c>
       <c r="H8" s="1">
-        <v>750</v>
+        <v>-1481</v>
       </c>
       <c r="I8" s="1">
-        <v>555</v>
+        <v>-214</v>
       </c>
       <c r="J8" s="1">
-        <v>770</v>
+        <v>-1300</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="B9" s="1">
-        <v>10757</v>
+        <v>297</v>
       </c>
       <c r="C9" s="1">
-        <v>9951</v>
+        <v>634</v>
       </c>
       <c r="D9" s="1">
-        <v>7847</v>
+        <v>-801</v>
       </c>
       <c r="E9" s="1">
-        <v>11128</v>
+        <v>-29</v>
       </c>
       <c r="F9" s="1">
-        <v>9953</v>
+        <v>1190</v>
       </c>
       <c r="G9" s="1">
-        <v>10482</v>
+        <v>412</v>
       </c>
       <c r="H9" s="1">
-        <v>9204</v>
+        <v>696</v>
       </c>
       <c r="I9" s="1">
-        <v>7520</v>
+        <v>211</v>
       </c>
       <c r="J9" s="1">
-        <v>6752</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10" s="1">
-        <v>-138</v>
+        <v>-1250</v>
       </c>
       <c r="C10" s="1">
-        <v>-1105</v>
+        <v>2223</v>
       </c>
       <c r="D10" s="1">
-        <v>2097</v>
+        <v>-451</v>
       </c>
       <c r="E10" s="1">
-        <v>-2436</v>
+        <v>-1278</v>
       </c>
       <c r="F10" s="1">
-        <v>-2339</v>
+        <v>459</v>
       </c>
       <c r="G10" s="1">
-        <v>-687</v>
+        <v>-331</v>
       </c>
       <c r="H10" s="1">
-        <v>-1481</v>
+        <v>2674</v>
       </c>
       <c r="I10" s="1">
-        <v>-214</v>
+        <v>301</v>
       </c>
       <c r="J10" s="1">
-        <v>-1300</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="1">
-        <v>2975</v>
-      </c>
-      <c r="D11" s="1">
-        <v>11391</v>
-      </c>
-      <c r="E11" s="1">
-        <v>6548</v>
-      </c>
-      <c r="F11" s="1">
-        <v>4974</v>
-      </c>
-      <c r="H11" s="1">
-        <v>3392</v>
-      </c>
-      <c r="I11" s="1">
-        <v>423</v>
-      </c>
-      <c r="J11" s="1">
-        <v>7716</v>
+        <v>-312</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" s="4" customFormat="1">
+      <c r="A11" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" s="4">
+        <v>11471</v>
+      </c>
+      <c r="E11" s="4">
+        <v>15433</v>
+      </c>
+      <c r="F11" s="4">
+        <v>29991</v>
+      </c>
+      <c r="G11" s="4">
+        <v>35384</v>
+      </c>
+      <c r="H11" s="4">
+        <v>33145</v>
+      </c>
+      <c r="I11" s="4">
+        <v>29432</v>
+      </c>
+      <c r="J11" s="4">
+        <v>22110</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="B12" s="1">
-        <v>26</v>
+        <v>8249</v>
       </c>
       <c r="C12" s="1">
-        <v>-19233</v>
+        <v>7079</v>
       </c>
       <c r="D12" s="1">
-        <v>1675</v>
+        <v>11144</v>
       </c>
       <c r="E12" s="1">
-        <v>8017</v>
+        <v>4827</v>
       </c>
       <c r="F12" s="1">
-        <v>19868</v>
+        <v>5865</v>
       </c>
       <c r="G12" s="1">
-        <v>20899</v>
+        <v>4194</v>
       </c>
       <c r="H12" s="1">
-        <v>21048</v>
+        <v>3019</v>
       </c>
       <c r="I12" s="1">
-        <v>21053</v>
+        <v>3433</v>
       </c>
       <c r="J12" s="1">
-        <v>9601</v>
+        <v>5560</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>63</v>
+        <v>9</v>
+      </c>
+      <c r="B13" s="1">
+        <v>6463</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1170</v>
       </c>
       <c r="D13" s="1">
-        <v>11471</v>
+        <v>-4065</v>
       </c>
       <c r="E13" s="1">
-        <v>15433</v>
+        <v>6317</v>
       </c>
       <c r="F13" s="1">
-        <v>29991</v>
+        <v>-1038</v>
       </c>
       <c r="G13" s="1">
-        <v>35384</v>
+        <v>1671</v>
       </c>
       <c r="H13" s="1">
-        <v>33145</v>
+        <v>1175</v>
       </c>
       <c r="I13" s="1">
-        <v>29432</v>
+        <v>-414</v>
       </c>
       <c r="J13" s="1">
-        <v>22110</v>
+        <v>-2127</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B14" s="1">
-        <v>-1250</v>
+        <v>771</v>
       </c>
       <c r="C14" s="1">
-        <v>2223</v>
+        <v>987</v>
       </c>
       <c r="D14" s="1">
-        <v>-451</v>
+        <v>1042</v>
       </c>
       <c r="E14" s="1">
-        <v>-1278</v>
+        <v>977</v>
       </c>
       <c r="F14" s="1">
-        <v>459</v>
+        <v>1020</v>
       </c>
       <c r="G14" s="1">
-        <v>-331</v>
+        <v>897</v>
       </c>
       <c r="H14" s="1">
-        <v>2674</v>
+        <v>750</v>
       </c>
       <c r="I14" s="1">
-        <v>301</v>
+        <v>555</v>
       </c>
       <c r="J14" s="1">
-        <v>-312</v>
+        <v>770</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B15" s="1">
-        <v>-24319</v>
+        <v>0</v>
       </c>
       <c r="C15" s="1">
-        <v>-37940</v>
+        <v>2975</v>
       </c>
       <c r="D15" s="1">
-        <v>-44414</v>
+        <v>11391</v>
       </c>
       <c r="E15" s="1">
-        <v>-43647</v>
+        <v>6548</v>
       </c>
       <c r="F15" s="1">
-        <v>-40554</v>
-      </c>
-      <c r="G15" s="1">
-        <v>-29239</v>
+        <v>4974</v>
+      </c>
+      <c r="H15" s="1">
+        <v>3392</v>
+      </c>
+      <c r="I15" s="1">
+        <v>423</v>
+      </c>
+      <c r="J15" s="1">
+        <v>7716</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="B16" s="1">
-        <v>2434</v>
+        <v>-24319</v>
       </c>
       <c r="C16" s="1">
-        <v>3410</v>
+        <v>-37940</v>
       </c>
       <c r="D16" s="1">
-        <v>3229</v>
+        <v>-44414</v>
       </c>
       <c r="E16" s="1">
-        <v>3128</v>
+        <v>-43647</v>
       </c>
       <c r="F16" s="1">
-        <v>2036</v>
+        <v>-40554</v>
       </c>
       <c r="G16" s="1">
-        <v>1854</v>
-      </c>
-      <c r="H16" s="1">
-        <v>1705</v>
-      </c>
-      <c r="I16" s="1">
-        <v>1546</v>
-      </c>
-      <c r="J16" s="1">
-        <v>1358</v>
+        <v>-29239</v>
       </c>
     </row>
   </sheetData>
@@ -4052,7 +4141,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="24" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="8" customHeight="1"/>
@@ -4061,7 +4150,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -4093,31 +4182,31 @@
         <v>9</v>
       </c>
       <c r="B4" s="1">
-        <v>9812</v>
+        <v>10605</v>
       </c>
       <c r="C4" s="1">
-        <v>6310</v>
+        <v>8589</v>
       </c>
       <c r="D4" s="1">
-        <v>2699</v>
+        <v>7280</v>
       </c>
       <c r="E4" s="1">
-        <v>1193</v>
+        <v>3389</v>
       </c>
       <c r="F4" s="1">
-        <v>1783</v>
+        <v>1990</v>
       </c>
       <c r="G4" s="1">
-        <v>1201</v>
+        <v>847</v>
       </c>
       <c r="H4" s="1">
-        <v>687</v>
+        <v>10896</v>
       </c>
       <c r="I4" s="1">
-        <v>687</v>
+        <v>10896</v>
       </c>
       <c r="J4" s="1">
-        <v>511</v>
+        <v>782</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -4125,191 +4214,191 @@
         <v>10</v>
       </c>
       <c r="B5" s="1">
-        <v>38466</v>
+        <v>51951</v>
       </c>
       <c r="C5" s="1">
-        <v>23065</v>
+        <v>34621</v>
       </c>
       <c r="D5" s="1">
-        <v>9999</v>
+        <v>18704</v>
       </c>
       <c r="E5" s="1">
-        <v>3827</v>
+        <v>9907</v>
       </c>
       <c r="F5" s="1">
-        <v>4650</v>
+        <v>19218</v>
       </c>
       <c r="G5" s="1">
-        <v>2429</v>
+        <v>10714</v>
       </c>
       <c r="H5" s="1">
-        <v>1657</v>
+        <v>1</v>
       </c>
       <c r="I5" s="1">
-        <v>1657</v>
+        <v>1</v>
       </c>
       <c r="J5" s="1">
-        <v>1424</v>
+        <v>6640</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>75</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1">
-        <v>21352</v>
+        <v>38466</v>
       </c>
       <c r="C6" s="1">
-        <v>11737</v>
+        <v>23065</v>
       </c>
       <c r="D6" s="1">
-        <v>6682</v>
+        <v>9999</v>
       </c>
       <c r="E6" s="1">
-        <v>4120</v>
+        <v>3827</v>
       </c>
       <c r="F6" s="1">
-        <v>2552</v>
+        <v>4650</v>
       </c>
       <c r="G6" s="1">
-        <v>1725</v>
+        <v>2429</v>
       </c>
       <c r="H6" s="1">
-        <v>1097</v>
+        <v>1657</v>
       </c>
       <c r="I6" s="1">
-        <v>1097</v>
+        <v>1657</v>
       </c>
       <c r="J6" s="1">
-        <v>818</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1">
-        <v>178</v>
+        <v>21403</v>
       </c>
       <c r="C7" s="1">
-        <v>28</v>
+        <v>10080</v>
       </c>
       <c r="D7" s="1">
-        <v>27</v>
+        <v>5282</v>
       </c>
       <c r="E7" s="1">
-        <v>-43</v>
+        <v>5159</v>
       </c>
       <c r="F7" s="1">
-        <v>-11</v>
+        <v>2605</v>
       </c>
       <c r="G7" s="1">
-        <v>19</v>
+        <v>1826</v>
       </c>
       <c r="H7" s="1">
-        <v>1</v>
+        <v>979</v>
       </c>
       <c r="I7" s="1">
-        <v>1</v>
+        <v>979</v>
       </c>
       <c r="J7" s="1">
-        <v>-12</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1">
-        <v>10118</v>
+        <v>3180</v>
       </c>
       <c r="C8" s="1">
-        <v>11237</v>
+        <v>3771</v>
       </c>
       <c r="D8" s="1">
-        <v>13132</v>
+        <v>3080</v>
       </c>
       <c r="E8" s="1">
-        <v>11971</v>
+        <v>791</v>
       </c>
       <c r="F8" s="1">
-        <v>10385</v>
+        <v>366</v>
       </c>
       <c r="G8" s="1">
-        <v>8721</v>
+        <v>239</v>
       </c>
       <c r="H8" s="1">
-        <v>7045</v>
+        <v>157</v>
       </c>
       <c r="I8" s="1">
-        <v>7045</v>
+        <v>157</v>
       </c>
       <c r="J8" s="1">
-        <v>6051</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="1">
-        <v>10605</v>
-      </c>
-      <c r="C9" s="1">
-        <v>8589</v>
-      </c>
-      <c r="D9" s="1">
-        <v>7280</v>
-      </c>
-      <c r="E9" s="1">
-        <v>3389</v>
-      </c>
-      <c r="F9" s="1">
-        <v>1990</v>
-      </c>
-      <c r="G9" s="1">
-        <v>847</v>
-      </c>
-      <c r="H9" s="1">
-        <v>10896</v>
-      </c>
-      <c r="I9" s="1">
-        <v>10896</v>
-      </c>
-      <c r="J9" s="1">
-        <v>782</v>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" s="4" customFormat="1">
+      <c r="A9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="4">
+        <v>125605</v>
+      </c>
+      <c r="C9" s="4">
+        <v>80126</v>
+      </c>
+      <c r="D9" s="4">
+        <v>44345</v>
+      </c>
+      <c r="E9" s="4">
+        <v>23073</v>
+      </c>
+      <c r="F9" s="4">
+        <v>28829</v>
+      </c>
+      <c r="G9" s="4">
+        <v>16055</v>
+      </c>
+      <c r="H9" s="4">
+        <v>13690</v>
+      </c>
+      <c r="I9" s="4">
+        <v>13690</v>
+      </c>
+      <c r="J9" s="4">
+        <v>10557</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1">
-        <v>24</v>
+        <v>10383</v>
       </c>
       <c r="C10" s="1">
-        <v>24</v>
+        <v>6283</v>
       </c>
       <c r="D10" s="1">
-        <v>2</v>
+        <v>3914</v>
       </c>
       <c r="E10" s="1">
-        <v>2</v>
+        <v>3807</v>
       </c>
       <c r="F10" s="1">
-        <v>3</v>
+        <v>2778</v>
       </c>
       <c r="G10" s="1">
-        <v>1</v>
+        <v>2149</v>
       </c>
       <c r="H10" s="1">
-        <v>1</v>
+        <v>1674</v>
       </c>
       <c r="I10" s="1">
-        <v>1</v>
+        <v>1674</v>
       </c>
       <c r="J10" s="1">
-        <v>1</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -4317,36 +4406,36 @@
         <v>76</v>
       </c>
       <c r="B11" s="1">
-        <v>13258</v>
+        <v>2867</v>
       </c>
       <c r="C11" s="1">
-        <v>10979</v>
+        <v>1793</v>
       </c>
       <c r="D11" s="1">
-        <v>6081</v>
+        <v>1346</v>
       </c>
       <c r="E11" s="1">
-        <v>3396</v>
+        <v>1038</v>
       </c>
       <c r="F11" s="1">
-        <v>1222</v>
+        <v>829</v>
       </c>
       <c r="G11" s="1">
-        <v>806</v>
+        <v>707</v>
       </c>
       <c r="H11" s="1">
-        <v>548</v>
+        <v>618</v>
       </c>
       <c r="I11" s="1">
-        <v>548</v>
+        <v>618</v>
       </c>
       <c r="J11" s="1">
-        <v>560</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1">
         <v>20832</v>
@@ -4410,34 +4499,34 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="B14" s="1">
-        <v>21403</v>
+        <v>13258</v>
       </c>
       <c r="C14" s="1">
-        <v>10080</v>
+        <v>10979</v>
       </c>
       <c r="D14" s="1">
-        <v>5282</v>
+        <v>6081</v>
       </c>
       <c r="E14" s="1">
-        <v>5159</v>
+        <v>3396</v>
       </c>
       <c r="F14" s="1">
-        <v>2605</v>
+        <v>1222</v>
       </c>
       <c r="G14" s="1">
-        <v>1826</v>
+        <v>806</v>
       </c>
       <c r="H14" s="1">
-        <v>979</v>
+        <v>548</v>
       </c>
       <c r="I14" s="1">
-        <v>979</v>
+        <v>548</v>
       </c>
       <c r="J14" s="1">
-        <v>1575</v>
+        <v>560</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -4445,124 +4534,127 @@
         <v>19</v>
       </c>
       <c r="B15" s="1">
-        <v>7469</v>
+        <v>8301</v>
       </c>
       <c r="C15" s="1">
-        <v>8463</v>
+        <v>6425</v>
       </c>
       <c r="D15" s="1">
-        <v>8459</v>
+        <v>4500</v>
       </c>
       <c r="E15" s="1">
-        <v>9703</v>
+        <v>3820</v>
       </c>
       <c r="F15" s="1">
-        <v>10946</v>
+        <v>3841</v>
       </c>
       <c r="G15" s="1">
-        <v>5964</v>
+        <v>2144</v>
       </c>
       <c r="H15" s="1">
-        <v>1991</v>
+        <v>118</v>
       </c>
       <c r="I15" s="1">
-        <v>1991</v>
+        <v>118</v>
       </c>
       <c r="J15" s="1">
-        <v>1988</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" s="4" customFormat="1">
+      <c r="A16" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="1">
-        <v>51951</v>
-      </c>
-      <c r="C16" s="1">
-        <v>34621</v>
-      </c>
-      <c r="D16" s="1">
-        <v>18704</v>
-      </c>
-      <c r="E16" s="1">
-        <v>9907</v>
-      </c>
-      <c r="F16" s="1">
-        <v>19218</v>
-      </c>
-      <c r="G16" s="1">
-        <v>10714</v>
-      </c>
-      <c r="H16" s="1">
-        <v>1</v>
-      </c>
-      <c r="I16" s="1">
-        <v>1</v>
-      </c>
-      <c r="J16" s="1">
-        <v>6640</v>
+      <c r="B16" s="4">
+        <v>206803</v>
+      </c>
+      <c r="C16" s="4">
+        <v>111601</v>
+      </c>
+      <c r="D16" s="4">
+        <v>65728</v>
+      </c>
+      <c r="E16" s="4">
+        <v>41182</v>
+      </c>
+      <c r="F16" s="4">
+        <v>44187</v>
+      </c>
+      <c r="G16" s="4">
+        <v>28791</v>
+      </c>
+      <c r="H16" s="4">
+        <v>17315</v>
+      </c>
+      <c r="I16" s="4">
+        <v>17315</v>
+      </c>
+      <c r="J16" s="4">
+        <v>13292</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="B17" s="1">
-        <v>2867</v>
+        <v>9812</v>
       </c>
       <c r="C17" s="1">
-        <v>1793</v>
+        <v>6310</v>
       </c>
       <c r="D17" s="1">
-        <v>1346</v>
+        <v>2699</v>
       </c>
       <c r="E17" s="1">
-        <v>1038</v>
+        <v>1193</v>
       </c>
       <c r="F17" s="1">
-        <v>829</v>
+        <v>1783</v>
       </c>
       <c r="G17" s="1">
-        <v>707</v>
+        <v>1201</v>
       </c>
       <c r="H17" s="1">
-        <v>618</v>
+        <v>687</v>
       </c>
       <c r="I17" s="1">
-        <v>618</v>
+        <v>687</v>
+      </c>
+      <c r="J17" s="1">
+        <v>511</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="B18" s="1">
-        <v>8301</v>
+        <v>21352</v>
       </c>
       <c r="C18" s="1">
-        <v>6425</v>
+        <v>11737</v>
       </c>
       <c r="D18" s="1">
-        <v>4500</v>
+        <v>6682</v>
       </c>
       <c r="E18" s="1">
-        <v>3820</v>
+        <v>4120</v>
       </c>
       <c r="F18" s="1">
-        <v>3841</v>
+        <v>2552</v>
       </c>
       <c r="G18" s="1">
-        <v>2144</v>
+        <v>1725</v>
       </c>
       <c r="H18" s="1">
-        <v>118</v>
+        <v>1097</v>
       </c>
       <c r="I18" s="1">
-        <v>118</v>
+        <v>1097</v>
       </c>
       <c r="J18" s="1">
-        <v>108</v>
+        <v>818</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -4570,370 +4662,370 @@
         <v>24</v>
       </c>
       <c r="B19" s="1">
-        <v>7306</v>
+        <v>999</v>
       </c>
       <c r="C19" s="1">
-        <v>4245</v>
+        <v>0</v>
       </c>
       <c r="D19" s="1">
-        <v>2541</v>
+        <v>1250</v>
       </c>
       <c r="E19" s="1">
-        <v>1913</v>
+        <v>1250</v>
       </c>
       <c r="F19" s="1">
-        <v>1553</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" t="s">
-        <v>67</v>
-      </c>
-      <c r="B20" s="1">
         <v>0</v>
       </c>
-      <c r="C20" s="1">
-        <v>0</v>
-      </c>
-      <c r="D20" s="1">
-        <v>0</v>
-      </c>
-      <c r="E20" s="1">
-        <v>0</v>
-      </c>
-      <c r="F20" s="1">
-        <v>0</v>
-      </c>
-      <c r="G20" s="1">
-        <v>0</v>
-      </c>
-      <c r="H20" s="1">
-        <v>0</v>
-      </c>
-      <c r="I20" s="1">
-        <v>0</v>
-      </c>
-      <c r="J20" s="1">
-        <v>0</v>
+      <c r="G19" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" s="4" customFormat="1">
+      <c r="A20" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="4">
+        <v>32163</v>
+      </c>
+      <c r="C20" s="4">
+        <v>18047</v>
+      </c>
+      <c r="D20" s="4">
+        <v>10631</v>
+      </c>
+      <c r="E20" s="4">
+        <v>6563</v>
+      </c>
+      <c r="F20" s="4">
+        <v>4335</v>
+      </c>
+      <c r="G20" s="4">
+        <v>3925</v>
+      </c>
+      <c r="H20" s="4">
+        <v>1784</v>
+      </c>
+      <c r="I20" s="4">
+        <v>1784</v>
+      </c>
+      <c r="J20" s="4">
+        <v>1329</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B21" s="1">
-        <v>3180</v>
+        <v>7469</v>
       </c>
       <c r="C21" s="1">
-        <v>3771</v>
+        <v>8463</v>
       </c>
       <c r="D21" s="1">
-        <v>3080</v>
+        <v>8459</v>
       </c>
       <c r="E21" s="1">
-        <v>791</v>
+        <v>9703</v>
       </c>
       <c r="F21" s="1">
-        <v>366</v>
+        <v>10946</v>
       </c>
       <c r="G21" s="1">
-        <v>239</v>
+        <v>5964</v>
       </c>
       <c r="H21" s="1">
-        <v>157</v>
+        <v>1991</v>
       </c>
       <c r="I21" s="1">
-        <v>157</v>
+        <v>1991</v>
       </c>
       <c r="J21" s="1">
-        <v>136</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B22" s="1">
-        <v>10383</v>
+        <v>7306</v>
       </c>
       <c r="C22" s="1">
-        <v>6283</v>
+        <v>4245</v>
       </c>
       <c r="D22" s="1">
-        <v>3914</v>
+        <v>2541</v>
       </c>
       <c r="E22" s="1">
-        <v>3807</v>
+        <v>1913</v>
       </c>
       <c r="F22" s="1">
-        <v>2778</v>
-      </c>
-      <c r="G22" s="1">
-        <v>2149</v>
-      </c>
-      <c r="H22" s="1">
-        <v>1674</v>
-      </c>
-      <c r="I22" s="1">
-        <v>1674</v>
-      </c>
-      <c r="J22" s="1">
-        <v>1404</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" s="1">
-        <v>146973</v>
-      </c>
-      <c r="C23" s="1">
-        <v>68038</v>
-      </c>
-      <c r="D23" s="1">
-        <v>29817</v>
-      </c>
-      <c r="E23" s="1">
-        <v>10171</v>
-      </c>
-      <c r="F23" s="1">
-        <v>16235</v>
-      </c>
-      <c r="G23" s="1">
-        <v>18908</v>
-      </c>
-      <c r="H23" s="1">
-        <v>14971</v>
-      </c>
-      <c r="I23" s="1">
-        <v>14971</v>
-      </c>
-      <c r="J23" s="1">
-        <v>12565</v>
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" s="4" customFormat="1">
+      <c r="A23" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B23" s="4">
+        <v>49510</v>
+      </c>
+      <c r="C23" s="4">
+        <v>32274</v>
+      </c>
+      <c r="D23" s="4">
+        <v>22750</v>
+      </c>
+      <c r="E23" s="4">
+        <v>19081</v>
+      </c>
+      <c r="F23" s="4">
+        <v>17575</v>
+      </c>
+      <c r="G23" s="4">
+        <v>11898</v>
+      </c>
+      <c r="H23" s="4">
+        <v>5111</v>
+      </c>
+      <c r="I23" s="4">
+        <v>5111</v>
+      </c>
+      <c r="J23" s="4">
+        <v>3950</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="B24" s="1">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="C24" s="1">
         <v>0</v>
       </c>
       <c r="D24" s="1">
-        <v>1250</v>
+        <v>0</v>
       </c>
       <c r="E24" s="1">
-        <v>1250</v>
+        <v>0</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>999</v>
+        <v>0</v>
+      </c>
+      <c r="H24" s="1">
+        <v>0</v>
+      </c>
+      <c r="I24" s="1">
+        <v>0</v>
+      </c>
+      <c r="J24" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B25" s="1">
-        <v>157293</v>
+        <v>24</v>
       </c>
       <c r="C25" s="1">
-        <v>79327</v>
+        <v>24</v>
       </c>
       <c r="D25" s="1">
-        <v>42978</v>
+        <v>2</v>
       </c>
       <c r="E25" s="1">
-        <v>22101</v>
+        <v>2</v>
       </c>
       <c r="F25" s="1">
-        <v>26612</v>
+        <v>3</v>
       </c>
       <c r="G25" s="1">
-        <v>16893</v>
+        <v>1</v>
       </c>
       <c r="H25" s="1">
-        <v>12204</v>
+        <v>1</v>
       </c>
       <c r="I25" s="1">
-        <v>12204</v>
+        <v>1</v>
       </c>
       <c r="J25" s="1">
-        <v>9342</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B26" s="1">
-        <v>206803</v>
+        <v>10118</v>
       </c>
       <c r="C26" s="1">
-        <v>111601</v>
+        <v>11237</v>
       </c>
       <c r="D26" s="1">
-        <v>65728</v>
+        <v>13132</v>
       </c>
       <c r="E26" s="1">
-        <v>41182</v>
+        <v>11971</v>
       </c>
       <c r="F26" s="1">
-        <v>44187</v>
+        <v>10385</v>
       </c>
       <c r="G26" s="1">
-        <v>28791</v>
+        <v>8721</v>
       </c>
       <c r="H26" s="1">
-        <v>17315</v>
+        <v>7045</v>
       </c>
       <c r="I26" s="1">
-        <v>17315</v>
+        <v>7045</v>
       </c>
       <c r="J26" s="1">
-        <v>13292</v>
+        <v>6051</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>33</v>
-      </c>
-      <c r="B27" s="1">
-        <v>125605</v>
-      </c>
-      <c r="C27" s="1">
-        <v>80126</v>
-      </c>
-      <c r="D27" s="1">
-        <v>44345</v>
-      </c>
-      <c r="E27" s="1">
-        <v>23073</v>
+        <v>30</v>
       </c>
       <c r="F27" s="1">
-        <v>28829</v>
+        <v>30</v>
       </c>
       <c r="G27" s="1">
-        <v>16055</v>
+        <v>-10756</v>
       </c>
       <c r="H27" s="1">
-        <v>13690</v>
+        <v>-9814</v>
       </c>
       <c r="I27" s="1">
-        <v>13690</v>
+        <v>-9814</v>
       </c>
       <c r="J27" s="1">
-        <v>10557</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B28" s="1">
-        <v>32163</v>
+        <v>178</v>
       </c>
       <c r="C28" s="1">
-        <v>18047</v>
+        <v>28</v>
       </c>
       <c r="D28" s="1">
-        <v>10631</v>
+        <v>27</v>
       </c>
       <c r="E28" s="1">
-        <v>6563</v>
+        <v>-43</v>
       </c>
       <c r="F28" s="1">
-        <v>4335</v>
+        <v>-11</v>
       </c>
       <c r="G28" s="1">
-        <v>3925</v>
+        <v>19</v>
       </c>
       <c r="H28" s="1">
-        <v>1784</v>
+        <v>1</v>
       </c>
       <c r="I28" s="1">
-        <v>1784</v>
+        <v>1</v>
       </c>
       <c r="J28" s="1">
-        <v>1329</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="B29" s="1">
-        <v>49510</v>
+        <v>146973</v>
       </c>
       <c r="C29" s="1">
-        <v>32274</v>
+        <v>68038</v>
       </c>
       <c r="D29" s="1">
-        <v>22750</v>
+        <v>29817</v>
       </c>
       <c r="E29" s="1">
-        <v>19081</v>
+        <v>10171</v>
       </c>
       <c r="F29" s="1">
-        <v>17575</v>
+        <v>16235</v>
       </c>
       <c r="G29" s="1">
-        <v>11898</v>
+        <v>18908</v>
       </c>
       <c r="H29" s="1">
-        <v>5111</v>
+        <v>14971</v>
       </c>
       <c r="I29" s="1">
-        <v>5111</v>
+        <v>14971</v>
       </c>
       <c r="J29" s="1">
-        <v>3950</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" t="s">
+        <v>12565</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" s="4" customFormat="1">
+      <c r="A30" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" s="4">
+        <v>157293</v>
+      </c>
+      <c r="C30" s="4">
+        <v>79327</v>
+      </c>
+      <c r="D30" s="4">
+        <v>42978</v>
+      </c>
+      <c r="E30" s="4">
+        <v>22101</v>
+      </c>
+      <c r="F30" s="4">
+        <v>26612</v>
+      </c>
+      <c r="G30" s="4">
+        <v>16893</v>
+      </c>
+      <c r="H30" s="4">
+        <v>12204</v>
+      </c>
+      <c r="I30" s="4">
+        <v>12204</v>
+      </c>
+      <c r="J30" s="4">
+        <v>9342</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" s="4" customFormat="1">
+      <c r="A31" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B31" s="4">
         <v>206803</v>
       </c>
-      <c r="C30" s="1">
+      <c r="C31" s="4">
         <v>111601</v>
       </c>
-      <c r="D30" s="1">
+      <c r="D31" s="4">
         <v>65728</v>
       </c>
-      <c r="E30" s="1">
+      <c r="E31" s="4">
         <v>41182</v>
       </c>
-      <c r="F30" s="1">
+      <c r="F31" s="4">
         <v>44187</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" t="s">
-        <v>36</v>
-      </c>
-      <c r="F31" s="1">
-        <v>30</v>
-      </c>
-      <c r="G31" s="1">
-        <v>345</v>
-      </c>
-      <c r="H31" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I31" s="1">
-        <v>342</v>
-      </c>
-      <c r="J31" s="1">
-        <v>2020</v>
       </c>
     </row>
   </sheetData>
@@ -4953,7 +5045,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="24" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="8" customHeight="1"/>
@@ -4962,7 +5054,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -4994,42 +5086,42 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B4" s="1">
-        <v>4.93</v>
+        <v>25</v>
       </c>
       <c r="C4" s="1">
-        <v>2.97</v>
+        <v>130497</v>
       </c>
       <c r="D4" s="1">
-        <v>12.05</v>
+        <v>60922</v>
       </c>
       <c r="E4" s="1">
-        <v>1.76</v>
+        <v>26974</v>
       </c>
       <c r="F4" s="1">
-        <v>3.91</v>
+        <v>26914</v>
       </c>
       <c r="G4" s="1">
-        <v>7.02</v>
+        <v>16675</v>
       </c>
       <c r="H4" s="1">
-        <v>1.15</v>
+        <v>10918</v>
       </c>
       <c r="I4" s="1">
-        <v>4.59</v>
+        <v>10918</v>
       </c>
       <c r="J4" s="1">
-        <v>6.81</v>
+        <v>11716</v>
       </c>
       <c r="K4" s="1">
-        <v>5.09</v>
+        <v>9714</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B5" s="1">
         <v>28.9</v>
@@ -5062,354 +5154,354 @@
         <v>3892</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
-      <c r="A6" t="s">
+    <row r="6" spans="1:11" s="4" customFormat="1">
+      <c r="A6" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="1">
-        <v>4.9</v>
-      </c>
-      <c r="C6" s="1">
-        <v>2.94</v>
-      </c>
-      <c r="D6" s="1">
-        <v>11.93</v>
-      </c>
-      <c r="E6" s="1">
-        <v>1.74</v>
-      </c>
-      <c r="F6" s="1">
-        <v>3.85</v>
-      </c>
-      <c r="G6" s="1">
-        <v>6.9</v>
-      </c>
-      <c r="H6" s="1">
-        <v>1.13</v>
-      </c>
-      <c r="I6" s="1">
-        <v>4.52</v>
-      </c>
-      <c r="J6" s="1">
-        <v>6.63</v>
-      </c>
-      <c r="K6" s="1">
-        <v>4.82</v>
+      <c r="B6" s="4">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="C6" s="4">
+        <v>97858</v>
+      </c>
+      <c r="D6" s="4">
+        <v>72.7</v>
+      </c>
+      <c r="E6" s="4">
+        <v>15356</v>
+      </c>
+      <c r="F6" s="4">
+        <v>17475</v>
+      </c>
+      <c r="G6" s="4">
+        <v>62.3</v>
+      </c>
+      <c r="H6" s="4">
+        <v>6768</v>
+      </c>
+      <c r="I6" s="4">
+        <v>6768</v>
+      </c>
+      <c r="J6" s="4">
+        <v>7171</v>
+      </c>
+      <c r="K6" s="4">
+        <v>5822</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B7" s="1">
-        <v>71.09999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="C7" s="1">
-        <v>97858</v>
+        <v>12914</v>
       </c>
       <c r="D7" s="1">
-        <v>72.7</v>
+        <v>14.2</v>
       </c>
       <c r="E7" s="1">
-        <v>15356</v>
+        <v>7339</v>
       </c>
       <c r="F7" s="1">
-        <v>17475</v>
+        <v>5268</v>
       </c>
       <c r="G7" s="1">
-        <v>62.3</v>
+        <v>23.5</v>
       </c>
       <c r="H7" s="1">
-        <v>6768</v>
+        <v>2829</v>
       </c>
       <c r="I7" s="1">
-        <v>6768</v>
+        <v>2829</v>
       </c>
       <c r="J7" s="1">
-        <v>7171</v>
+        <v>2376</v>
       </c>
       <c r="K7" s="1">
-        <v>5822</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B8" s="1">
-        <v>141450</v>
-      </c>
-      <c r="C8" s="1">
-        <v>84026</v>
-      </c>
-      <c r="D8" s="1">
-        <v>33818</v>
-      </c>
-      <c r="E8" s="1">
-        <v>4181</v>
-      </c>
-      <c r="F8" s="1">
-        <v>9941</v>
-      </c>
-      <c r="G8" s="1">
-        <v>4409</v>
-      </c>
-      <c r="H8" s="1">
-        <v>2970</v>
-      </c>
-      <c r="I8" s="1">
-        <v>2970</v>
-      </c>
-      <c r="J8" s="1">
-        <v>3896</v>
-      </c>
-      <c r="K8" s="1">
-        <v>3196</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" t="s">
-        <v>80</v>
-      </c>
-      <c r="B9" s="1">
-        <v>9.9</v>
-      </c>
-      <c r="C9" s="1">
-        <v>11146</v>
-      </c>
-      <c r="D9" s="1">
-        <v>6.6</v>
-      </c>
-      <c r="E9" s="1">
-        <v>-187</v>
-      </c>
-      <c r="F9" s="1">
-        <v>189</v>
-      </c>
-      <c r="G9" s="1">
-        <v>26.5</v>
-      </c>
-      <c r="H9" s="1">
-        <v>174</v>
-      </c>
-      <c r="I9" s="1">
-        <v>174</v>
-      </c>
-      <c r="J9" s="1">
-        <v>-245</v>
-      </c>
-      <c r="K9" s="1">
-        <v>149</v>
+        <v>1797</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" s="4" customFormat="1">
+      <c r="A8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="4">
+        <v>10.7</v>
+      </c>
+      <c r="C8" s="4">
+        <v>16405</v>
+      </c>
+      <c r="D8" s="4">
+        <v>18.6</v>
+      </c>
+      <c r="E8" s="4">
+        <v>11132</v>
+      </c>
+      <c r="F8" s="4">
+        <v>7434</v>
+      </c>
+      <c r="G8" s="4">
+        <v>35.1</v>
+      </c>
+      <c r="H8" s="4">
+        <v>3922</v>
+      </c>
+      <c r="I8" s="4">
+        <v>3922</v>
+      </c>
+      <c r="J8" s="4">
+        <v>3367</v>
+      </c>
+      <c r="K8" s="4">
+        <v>2612</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="4" customFormat="1">
+      <c r="A9" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="4">
+        <v>60.4</v>
+      </c>
+      <c r="C9" s="4">
+        <v>81453</v>
+      </c>
+      <c r="D9" s="4">
+        <v>54.1</v>
+      </c>
+      <c r="E9" s="4">
+        <v>4224</v>
+      </c>
+      <c r="F9" s="4">
+        <v>10041</v>
+      </c>
+      <c r="G9" s="4">
+        <v>27.2</v>
+      </c>
+      <c r="H9" s="4">
+        <v>2846</v>
+      </c>
+      <c r="I9" s="4">
+        <v>2846</v>
+      </c>
+      <c r="J9" s="4">
+        <v>3804</v>
+      </c>
+      <c r="K9" s="4">
+        <v>3210</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="B10" s="1">
-        <v>-0.1</v>
+        <v>1.1</v>
       </c>
       <c r="C10" s="1">
-        <v>-247</v>
+        <v>1786</v>
       </c>
       <c r="D10" s="1">
-        <v>-0.4</v>
+        <v>1.4</v>
       </c>
       <c r="E10" s="1">
-        <v>-262</v>
+        <v>267</v>
       </c>
       <c r="F10" s="1">
-        <v>-236</v>
+        <v>29</v>
       </c>
       <c r="G10" s="1">
-        <v>-1.1</v>
+        <v>0.3</v>
       </c>
       <c r="H10" s="1">
-        <v>-52</v>
+        <v>178</v>
       </c>
       <c r="I10" s="1">
-        <v>-52</v>
+        <v>178</v>
       </c>
       <c r="J10" s="1">
-        <v>-58</v>
+        <v>136</v>
       </c>
       <c r="K10" s="1">
-        <v>-61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="B11" s="1">
-        <v>1.1</v>
+        <v>-0.1</v>
       </c>
       <c r="C11" s="1">
-        <v>1786</v>
+        <v>-247</v>
       </c>
       <c r="D11" s="1">
-        <v>1.4</v>
+        <v>-0.4</v>
       </c>
       <c r="E11" s="1">
-        <v>267</v>
+        <v>-262</v>
       </c>
       <c r="F11" s="1">
-        <v>29</v>
+        <v>-236</v>
       </c>
       <c r="G11" s="1">
-        <v>0.3</v>
+        <v>-1.1</v>
       </c>
       <c r="H11" s="1">
-        <v>178</v>
+        <v>-52</v>
       </c>
       <c r="I11" s="1">
-        <v>178</v>
+        <v>-52</v>
       </c>
       <c r="J11" s="1">
-        <v>136</v>
+        <v>-58</v>
       </c>
       <c r="K11" s="1">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" t="s">
-        <v>50</v>
-      </c>
-      <c r="B12" s="1">
-        <v>55.6</v>
-      </c>
-      <c r="C12" s="1">
-        <v>72880</v>
-      </c>
-      <c r="D12" s="1">
-        <v>48.9</v>
-      </c>
-      <c r="E12" s="1">
-        <v>4368</v>
-      </c>
-      <c r="F12" s="1">
-        <v>9752</v>
-      </c>
-      <c r="G12" s="1">
-        <v>26</v>
-      </c>
-      <c r="H12" s="1">
-        <v>2796</v>
-      </c>
-      <c r="I12" s="1">
-        <v>2796</v>
-      </c>
-      <c r="J12" s="1">
-        <v>4141</v>
-      </c>
-      <c r="K12" s="1">
-        <v>3047</v>
+        <v>-61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" s="4" customFormat="1">
+      <c r="A12" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" s="4">
+        <v>141450</v>
+      </c>
+      <c r="C12" s="4">
+        <v>84026</v>
+      </c>
+      <c r="D12" s="4">
+        <v>33818</v>
+      </c>
+      <c r="E12" s="4">
+        <v>4181</v>
+      </c>
+      <c r="F12" s="4">
+        <v>9941</v>
+      </c>
+      <c r="G12" s="4">
+        <v>4409</v>
+      </c>
+      <c r="H12" s="4">
+        <v>2970</v>
+      </c>
+      <c r="I12" s="4">
+        <v>2970</v>
+      </c>
+      <c r="J12" s="4">
+        <v>3896</v>
+      </c>
+      <c r="K12" s="4">
+        <v>3196</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="B13" s="1">
-        <v>60.4</v>
+        <v>9.9</v>
       </c>
       <c r="C13" s="1">
-        <v>81453</v>
+        <v>11146</v>
       </c>
       <c r="D13" s="1">
-        <v>54.1</v>
+        <v>6.6</v>
       </c>
       <c r="E13" s="1">
-        <v>4224</v>
+        <v>-187</v>
       </c>
       <c r="F13" s="1">
-        <v>10041</v>
+        <v>189</v>
       </c>
       <c r="G13" s="1">
-        <v>27.2</v>
+        <v>26.5</v>
       </c>
       <c r="H13" s="1">
-        <v>2846</v>
+        <v>174</v>
       </c>
       <c r="I13" s="1">
-        <v>2846</v>
+        <v>174</v>
       </c>
       <c r="J13" s="1">
-        <v>3804</v>
+        <v>-245</v>
       </c>
       <c r="K13" s="1">
-        <v>3210</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" t="s">
-        <v>52</v>
-      </c>
-      <c r="B14" s="1">
-        <v>8.6</v>
-      </c>
-      <c r="C14" s="1">
-        <v>12914</v>
-      </c>
-      <c r="D14" s="1">
-        <v>14.2</v>
-      </c>
-      <c r="E14" s="1">
-        <v>7339</v>
-      </c>
-      <c r="F14" s="1">
-        <v>5268</v>
-      </c>
-      <c r="G14" s="1">
-        <v>23.5</v>
-      </c>
-      <c r="H14" s="1">
-        <v>2829</v>
-      </c>
-      <c r="I14" s="1">
-        <v>2829</v>
-      </c>
-      <c r="J14" s="1">
-        <v>2376</v>
-      </c>
-      <c r="K14" s="1">
-        <v>1797</v>
+        <v>149</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" s="4" customFormat="1">
+      <c r="A14" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="4">
+        <v>55.6</v>
+      </c>
+      <c r="C14" s="4">
+        <v>72880</v>
+      </c>
+      <c r="D14" s="4">
+        <v>48.9</v>
+      </c>
+      <c r="E14" s="4">
+        <v>4368</v>
+      </c>
+      <c r="F14" s="4">
+        <v>9752</v>
+      </c>
+      <c r="G14" s="4">
+        <v>26</v>
+      </c>
+      <c r="H14" s="4">
+        <v>2796</v>
+      </c>
+      <c r="I14" s="4">
+        <v>2796</v>
+      </c>
+      <c r="J14" s="4">
+        <v>4141</v>
+      </c>
+      <c r="K14" s="4">
+        <v>3047</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B15" s="1">
-        <v>25</v>
+        <v>4.93</v>
       </c>
       <c r="C15" s="1">
-        <v>130497</v>
+        <v>2.97</v>
       </c>
       <c r="D15" s="1">
-        <v>28</v>
+        <v>12.05</v>
       </c>
       <c r="E15" s="1">
-        <v>26974</v>
+        <v>1.76</v>
       </c>
       <c r="F15" s="1">
-        <v>26914</v>
+        <v>3.91</v>
       </c>
       <c r="G15" s="1">
-        <v>100</v>
+        <v>7.02</v>
       </c>
       <c r="H15" s="1">
-        <v>10918</v>
+        <v>1.15</v>
       </c>
       <c r="I15" s="1">
-        <v>10918</v>
+        <v>4.59</v>
       </c>
       <c r="J15" s="1">
-        <v>11716</v>
+        <v>6.81</v>
       </c>
       <c r="K15" s="1">
-        <v>9714</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -5417,34 +5509,34 @@
         <v>55</v>
       </c>
       <c r="B16" s="1">
-        <v>10.7</v>
+        <v>4.9</v>
       </c>
       <c r="C16" s="1">
-        <v>16405</v>
+        <v>2.94</v>
       </c>
       <c r="D16" s="1">
-        <v>18.6</v>
+        <v>11.93</v>
       </c>
       <c r="E16" s="1">
-        <v>11132</v>
+        <v>1.74</v>
       </c>
       <c r="F16" s="1">
-        <v>7434</v>
+        <v>3.85</v>
       </c>
       <c r="G16" s="1">
-        <v>35.1</v>
+        <v>6.9</v>
       </c>
       <c r="H16" s="1">
-        <v>3922</v>
+        <v>1.13</v>
       </c>
       <c r="I16" s="1">
-        <v>3922</v>
+        <v>4.52</v>
       </c>
       <c r="J16" s="1">
-        <v>3367</v>
+        <v>6.63</v>
       </c>
       <c r="K16" s="1">
-        <v>2612</v>
+        <v>4.82</v>
       </c>
     </row>
   </sheetData>
@@ -5464,7 +5556,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="24" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="8" customHeight="1"/>
@@ -5473,7 +5565,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -5503,540 +5595,549 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="1">
-        <v>3096</v>
-      </c>
-      <c r="C4" s="1">
-        <v>3357</v>
-      </c>
-      <c r="D4" s="1">
-        <v>1531</v>
-      </c>
-      <c r="E4" s="1">
-        <v>-551</v>
-      </c>
-      <c r="F4" s="1">
-        <v>568</v>
-      </c>
-      <c r="G4" s="1">
-        <v>363</v>
-      </c>
-      <c r="H4" s="1">
-        <v>194</v>
-      </c>
-      <c r="I4" s="1">
-        <v>194</v>
-      </c>
-      <c r="J4" s="1">
-        <v>-135</v>
-      </c>
-      <c r="K4" s="1">
-        <v>90</v>
+    <row r="4" spans="1:11" s="4" customFormat="1">
+      <c r="A4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>120067</v>
+      </c>
+      <c r="C4" s="4">
+        <v>72880</v>
+      </c>
+      <c r="D4" s="4">
+        <v>29760</v>
+      </c>
+      <c r="E4" s="4">
+        <v>4368</v>
+      </c>
+      <c r="F4" s="4">
+        <v>9752</v>
+      </c>
+      <c r="G4" s="4">
+        <v>4332</v>
+      </c>
+      <c r="H4" s="4">
+        <v>2796</v>
+      </c>
+      <c r="I4" s="4">
+        <v>2796</v>
+      </c>
+      <c r="J4" s="4">
+        <v>4141</v>
+      </c>
+      <c r="K4" s="4">
+        <v>3047</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="B5" s="1">
-        <v>-15399</v>
+        <v>2843</v>
       </c>
       <c r="C5" s="1">
-        <v>-13063</v>
+        <v>1864</v>
       </c>
       <c r="D5" s="1">
-        <v>-6172</v>
+        <v>1508</v>
       </c>
       <c r="E5" s="1">
-        <v>822</v>
+        <v>1544</v>
       </c>
       <c r="F5" s="1">
-        <v>-2215</v>
+        <v>1174</v>
       </c>
       <c r="G5" s="1">
-        <v>-550</v>
+        <v>1098</v>
       </c>
       <c r="H5" s="1">
-        <v>-233</v>
+        <v>381</v>
       </c>
       <c r="I5" s="1">
-        <v>-233</v>
+        <v>381</v>
       </c>
       <c r="J5" s="1">
-        <v>-149</v>
+        <v>262</v>
       </c>
       <c r="K5" s="1">
-        <v>-440</v>
+        <v>199</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B6" s="1">
-        <v>5257</v>
+        <v>6386</v>
       </c>
       <c r="C6" s="1">
-        <v>4278</v>
+        <v>4737</v>
       </c>
       <c r="D6" s="1">
-        <v>2025</v>
+        <v>3549</v>
       </c>
       <c r="E6" s="1">
-        <v>1341</v>
+        <v>2709</v>
       </c>
       <c r="F6" s="1">
-        <v>581</v>
+        <v>2004</v>
       </c>
       <c r="G6" s="1">
-        <v>290</v>
+        <v>1397</v>
+      </c>
+      <c r="H6" s="1">
+        <v>844</v>
+      </c>
+      <c r="I6" s="1">
+        <v>844</v>
+      </c>
+      <c r="J6" s="1">
+        <v>557</v>
+      </c>
+      <c r="K6" s="1">
+        <v>391</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>59</v>
+      </c>
+      <c r="B7" s="1">
+        <v>-1424</v>
+      </c>
+      <c r="C7" s="1">
+        <v>-4477</v>
+      </c>
+      <c r="D7" s="1">
+        <v>-2489</v>
+      </c>
+      <c r="E7" s="1">
+        <v>-2164</v>
+      </c>
+      <c r="F7" s="1">
+        <v>-406</v>
+      </c>
+      <c r="G7" s="1">
+        <v>-282</v>
+      </c>
+      <c r="H7" s="1">
+        <v>18</v>
       </c>
       <c r="I7" s="1">
-        <v>-489</v>
+        <v>18</v>
       </c>
       <c r="J7" s="1">
-        <v>-600</v>
+        <v>-315</v>
       </c>
       <c r="K7" s="1">
-        <v>-593</v>
+        <v>-359</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B8" s="1">
-        <v>2016</v>
+        <v>-15399</v>
       </c>
       <c r="C8" s="1">
-        <v>1309</v>
+        <v>-13063</v>
       </c>
       <c r="D8" s="1">
-        <v>3891</v>
+        <v>-6172</v>
       </c>
       <c r="E8" s="1">
-        <v>1399</v>
+        <v>822</v>
       </c>
       <c r="F8" s="1">
-        <v>1143</v>
+        <v>-2215</v>
       </c>
       <c r="G8" s="1">
-        <v>-10049</v>
+        <v>-550</v>
       </c>
       <c r="H8" s="1">
-        <v>10114</v>
+        <v>-233</v>
       </c>
       <c r="I8" s="1">
-        <v>10114</v>
+        <v>-233</v>
       </c>
       <c r="J8" s="1">
-        <v>-3220</v>
+        <v>-149</v>
       </c>
       <c r="K8" s="1">
-        <v>2236</v>
+        <v>-440</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="B9" s="1">
-        <v>10605</v>
+        <v>-11324</v>
       </c>
       <c r="C9" s="1">
-        <v>8589</v>
+        <v>-4781</v>
       </c>
       <c r="D9" s="1">
-        <v>7280</v>
+        <v>-98</v>
       </c>
       <c r="E9" s="1">
-        <v>3389</v>
+        <v>-2554</v>
       </c>
       <c r="F9" s="1">
-        <v>1990</v>
+        <v>-774</v>
       </c>
       <c r="G9" s="1">
-        <v>847</v>
+        <v>-524</v>
+      </c>
+      <c r="H9" s="1">
+        <v>597</v>
+      </c>
+      <c r="I9" s="1">
+        <v>597</v>
+      </c>
+      <c r="J9" s="1">
+        <v>-776</v>
+      </c>
+      <c r="K9" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B10" s="1">
-        <v>-40086</v>
+        <v>3096</v>
       </c>
       <c r="C10" s="1">
-        <v>-33706</v>
+        <v>3357</v>
       </c>
       <c r="D10" s="1">
-        <v>-9533</v>
+        <v>1531</v>
       </c>
       <c r="E10" s="1">
-        <v>-10039</v>
+        <v>-551</v>
+      </c>
+      <c r="F10" s="1">
+        <v>568</v>
+      </c>
+      <c r="G10" s="1">
+        <v>363</v>
+      </c>
+      <c r="H10" s="1">
+        <v>194</v>
+      </c>
+      <c r="I10" s="1">
+        <v>194</v>
+      </c>
+      <c r="J10" s="1">
+        <v>-135</v>
+      </c>
+      <c r="K10" s="1">
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1">
-        <v>-1424</v>
+        <v>577</v>
       </c>
       <c r="C11" s="1">
-        <v>-4477</v>
+        <v>-395</v>
       </c>
       <c r="D11" s="1">
-        <v>-2489</v>
+        <v>-1522</v>
       </c>
       <c r="E11" s="1">
-        <v>-2164</v>
+        <v>-1517</v>
       </c>
       <c r="F11" s="1">
-        <v>-406</v>
+        <v>-1715</v>
       </c>
       <c r="G11" s="1">
-        <v>-282</v>
+        <v>-394</v>
       </c>
       <c r="H11" s="1">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="I11" s="1">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="J11" s="1">
-        <v>-315</v>
+        <v>-55</v>
       </c>
       <c r="K11" s="1">
-        <v>-359</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" t="s">
-        <v>59</v>
-      </c>
-      <c r="B12" s="1">
-        <v>2843</v>
-      </c>
-      <c r="C12" s="1">
-        <v>1864</v>
-      </c>
-      <c r="D12" s="1">
-        <v>1508</v>
-      </c>
-      <c r="E12" s="1">
-        <v>1544</v>
-      </c>
-      <c r="F12" s="1">
-        <v>1174</v>
-      </c>
-      <c r="G12" s="1">
-        <v>1098</v>
-      </c>
-      <c r="H12" s="1">
-        <v>381</v>
-      </c>
-      <c r="I12" s="1">
-        <v>381</v>
-      </c>
-      <c r="J12" s="1">
-        <v>262</v>
-      </c>
-      <c r="K12" s="1">
-        <v>199</v>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" s="4" customFormat="1">
+      <c r="A12" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" s="4">
+        <v>102718</v>
+      </c>
+      <c r="C12" s="4">
+        <v>64089</v>
+      </c>
+      <c r="D12" s="4">
+        <v>28090</v>
+      </c>
+      <c r="E12" s="4">
+        <v>5641</v>
+      </c>
+      <c r="F12" s="4">
+        <v>9108</v>
+      </c>
+      <c r="G12" s="4">
+        <v>5822</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>60</v>
-      </c>
-      <c r="B13" s="1">
+        <v>61</v>
+      </c>
+      <c r="I13" s="1">
+        <v>-489</v>
+      </c>
+      <c r="J13" s="1">
+        <v>-600</v>
+      </c>
+      <c r="K13" s="1">
+        <v>-593</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" s="4" customFormat="1">
+      <c r="A14" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" s="4">
+        <v>-52228</v>
+      </c>
+      <c r="C14" s="4">
+        <v>-20421</v>
+      </c>
+      <c r="D14" s="4">
+        <v>-10566</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" s="4" customFormat="1">
+      <c r="A15" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" s="4">
+        <v>10605</v>
+      </c>
+      <c r="C15" s="4">
+        <v>8589</v>
+      </c>
+      <c r="D15" s="4">
+        <v>7280</v>
+      </c>
+      <c r="E15" s="4">
+        <v>3389</v>
+      </c>
+      <c r="F15" s="4">
+        <v>1990</v>
+      </c>
+      <c r="G15" s="4">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" s="4" customFormat="1">
+      <c r="A16" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" s="4">
         <v>-48474</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C16" s="4">
         <v>-42359</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D16" s="4">
         <v>-13633</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E16" s="4">
         <v>-11617</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="1">
-        <v>-11324</v>
-      </c>
-      <c r="C14" s="1">
-        <v>-4781</v>
-      </c>
-      <c r="D14" s="1">
-        <v>-98</v>
-      </c>
-      <c r="E14" s="1">
-        <v>-2554</v>
-      </c>
-      <c r="F14" s="1">
-        <v>-774</v>
-      </c>
-      <c r="G14" s="1">
-        <v>-524</v>
-      </c>
-      <c r="H14" s="1">
-        <v>597</v>
-      </c>
-      <c r="I14" s="1">
-        <v>597</v>
-      </c>
-      <c r="J14" s="1">
-        <v>-776</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" t="s">
-        <v>61</v>
-      </c>
-      <c r="B15" s="1">
-        <v>-52228</v>
-      </c>
-      <c r="C15" s="1">
-        <v>-20421</v>
-      </c>
-      <c r="D15" s="1">
-        <v>-10566</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="1">
-        <v>15157</v>
-      </c>
-      <c r="C16" s="1">
-        <v>11195</v>
-      </c>
-      <c r="D16" s="1">
-        <v>9732</v>
-      </c>
-      <c r="E16" s="1">
-        <v>19425</v>
-      </c>
-      <c r="F16" s="1">
-        <v>-24787</v>
-      </c>
-      <c r="G16" s="1">
-        <v>-19308</v>
-      </c>
-      <c r="H16" s="1">
-        <v>-1461</v>
-      </c>
-      <c r="I16" s="1">
-        <v>-1461</v>
-      </c>
-      <c r="J16" s="1">
-        <v>-11148</v>
-      </c>
-      <c r="K16" s="1">
-        <v>-36</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="B17" s="1">
-        <v>120067</v>
+        <v>5257</v>
       </c>
       <c r="C17" s="1">
-        <v>72880</v>
+        <v>4278</v>
       </c>
       <c r="D17" s="1">
-        <v>29760</v>
+        <v>2025</v>
       </c>
       <c r="E17" s="1">
-        <v>4368</v>
+        <v>1341</v>
       </c>
       <c r="F17" s="1">
-        <v>9752</v>
+        <v>581</v>
       </c>
       <c r="G17" s="1">
-        <v>4332</v>
-      </c>
-      <c r="H17" s="1">
-        <v>2796</v>
-      </c>
-      <c r="I17" s="1">
-        <v>2796</v>
-      </c>
-      <c r="J17" s="1">
-        <v>4141</v>
-      </c>
-      <c r="K17" s="1">
-        <v>3047</v>
+        <v>290</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="B18" s="1">
-        <v>102718</v>
+        <v>2016</v>
       </c>
       <c r="C18" s="1">
-        <v>64089</v>
+        <v>1309</v>
       </c>
       <c r="D18" s="1">
-        <v>28090</v>
+        <v>3891</v>
       </c>
       <c r="E18" s="1">
-        <v>5641</v>
+        <v>1399</v>
       </c>
       <c r="F18" s="1">
-        <v>9108</v>
+        <v>1143</v>
       </c>
       <c r="G18" s="1">
-        <v>5822</v>
+        <v>-10049</v>
+      </c>
+      <c r="H18" s="1">
+        <v>10114</v>
+      </c>
+      <c r="I18" s="1">
+        <v>10114</v>
+      </c>
+      <c r="J18" s="1">
+        <v>-3220</v>
+      </c>
+      <c r="K18" s="1">
+        <v>2236</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B19" s="1">
-        <v>577</v>
+        <v>-40086</v>
       </c>
       <c r="C19" s="1">
-        <v>-395</v>
+        <v>-33706</v>
       </c>
       <c r="D19" s="1">
-        <v>-1522</v>
+        <v>-9533</v>
       </c>
       <c r="E19" s="1">
-        <v>-1517</v>
+        <v>-10039</v>
       </c>
       <c r="F19" s="1">
-        <v>-1715</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>-394</v>
-      </c>
-      <c r="H19" s="1">
-        <v>77</v>
-      </c>
-      <c r="I19" s="1">
-        <v>77</v>
-      </c>
-      <c r="J19" s="1">
-        <v>-55</v>
-      </c>
-      <c r="K19" s="1">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="B20" s="1">
-        <v>1844</v>
+        <v>15157</v>
       </c>
       <c r="C20" s="1">
-        <v>1221</v>
+        <v>11195</v>
       </c>
       <c r="D20" s="1">
-        <v>514</v>
+        <v>9732</v>
       </c>
       <c r="E20" s="1">
-        <v>252</v>
+        <v>19425</v>
       </c>
       <c r="F20" s="1">
-        <v>192</v>
+        <v>-24787</v>
       </c>
       <c r="G20" s="1">
-        <v>163</v>
+        <v>-19308</v>
       </c>
       <c r="H20" s="1">
-        <v>28</v>
+        <v>-1461</v>
       </c>
       <c r="I20" s="1">
-        <v>28</v>
+        <v>-1461</v>
       </c>
       <c r="J20" s="1">
-        <v>2</v>
+        <v>-11148</v>
       </c>
       <c r="K20" s="1">
-        <v>481</v>
+        <v>-36</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B21" s="1">
-        <v>-6042</v>
+        <v>1844</v>
       </c>
       <c r="C21" s="1">
-        <v>-3236</v>
+        <v>1221</v>
       </c>
       <c r="D21" s="1">
-        <v>-1069</v>
+        <v>514</v>
       </c>
       <c r="E21" s="1">
-        <v>-1833</v>
+        <v>252</v>
       </c>
       <c r="F21" s="1">
-        <v>-976</v>
+        <v>192</v>
       </c>
       <c r="G21" s="1">
-        <v>-1128</v>
+        <v>163</v>
+      </c>
+      <c r="H21" s="1">
+        <v>28</v>
+      </c>
+      <c r="I21" s="1">
+        <v>28</v>
+      </c>
+      <c r="J21" s="1">
+        <v>2</v>
+      </c>
+      <c r="K21" s="1">
+        <v>481</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="B22" s="1">
-        <v>6386</v>
+        <v>-6042</v>
       </c>
       <c r="C22" s="1">
-        <v>4737</v>
+        <v>-3236</v>
       </c>
       <c r="D22" s="1">
-        <v>3549</v>
+        <v>-1069</v>
       </c>
       <c r="E22" s="1">
-        <v>2709</v>
+        <v>-1833</v>
       </c>
       <c r="F22" s="1">
-        <v>2004</v>
+        <v>-976</v>
       </c>
       <c r="G22" s="1">
-        <v>1397</v>
-      </c>
-      <c r="H22" s="1">
-        <v>844</v>
-      </c>
-      <c r="I22" s="1">
-        <v>844</v>
-      </c>
-      <c r="J22" s="1">
-        <v>557</v>
-      </c>
-      <c r="K22" s="1">
-        <v>391</v>
+        <v>-1128</v>
       </c>
     </row>
   </sheetData>

--- a/10k_financial_statements.xlsx
+++ b/10k_financial_statements.xlsx
@@ -23,17 +23,17 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'AMD - Income statement'!$A$3:$J$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Intel - Balance sheet'!$A$3:$I$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Intel - Cash flow statement'!$A$3:$J$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Intel - Income statement'!$A$3:$J$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Intel - Income statement'!$A$3:$J$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'NVIDIA - Balance sheet'!$A$3:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'NVIDIA - Cash flow statement'!$A$3:$K$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'NVIDIA - Income statement'!$A$3:$K$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'NVIDIA - Income statement'!$A$3:$K$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="89">
   <si>
     <t>Line item</t>
   </si>
@@ -149,6 +149,9 @@
     <t>AMD - Balance sheet</t>
   </si>
   <si>
+    <t>Amounts in USD millions, except per-share data and share counts</t>
+  </si>
+  <si>
     <t>FY 2017</t>
   </si>
   <si>
@@ -249,6 +252,12 @@
   </si>
   <si>
     <t>Net income attributable to non-controlling interests</t>
+  </si>
+  <si>
+    <t>Weighted average shares used in basic EPS</t>
+  </si>
+  <si>
+    <t>Weighted average shares used in diluted EPS</t>
   </si>
   <si>
     <t>Intel - Income statement</t>
@@ -300,7 +309,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00;[Red](#,##0.00)"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -312,6 +321,14 @@
       <b/>
       <sz val="16"/>
       <color rgb="FF17365D"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF666666"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -368,12 +385,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -680,33 +698,37 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="8" customHeight="1"/>
+    <row r="2" spans="1:9" ht="18" customHeight="1">
+      <c r="A2" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>8</v>
       </c>
     </row>
@@ -863,32 +885,32 @@
         <v>270</v>
       </c>
     </row>
-    <row r="10" spans="1:9" s="4" customFormat="1">
-      <c r="A10" s="4" t="s">
+    <row r="10" spans="1:9" s="5" customFormat="1">
+      <c r="A10" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="5">
         <v>26947</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="5">
         <v>19049</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="5">
         <v>16768</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="5">
         <v>15019</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="5">
         <v>8583</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G10" s="5">
         <v>6143</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H10" s="5">
         <v>4597</v>
       </c>
-      <c r="I10" s="4">
+      <c r="I10" s="5">
         <v>3540</v>
       </c>
     </row>
@@ -987,32 +1009,32 @@
         <v>321</v>
       </c>
     </row>
-    <row r="15" spans="1:9" s="4" customFormat="1">
-      <c r="A15" s="4" t="s">
+    <row r="15" spans="1:9" s="5" customFormat="1">
+      <c r="A15" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="5">
         <v>76926</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="5">
         <v>69226</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="5">
         <v>67885</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="5">
         <v>67580</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="5">
         <v>12419</v>
       </c>
-      <c r="G15" s="4">
+      <c r="G15" s="5">
         <v>8962</v>
       </c>
-      <c r="H15" s="4">
+      <c r="H15" s="5">
         <v>6028</v>
       </c>
-      <c r="I15" s="4">
+      <c r="I15" s="5">
         <v>4556</v>
       </c>
     </row>
@@ -1108,32 +1130,32 @@
         <v>136</v>
       </c>
     </row>
-    <row r="20" spans="1:9" s="4" customFormat="1">
-      <c r="A20" s="4" t="s">
+    <row r="20" spans="1:9" s="5" customFormat="1">
+      <c r="A20" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" s="5">
         <v>9455</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="5">
         <v>7281</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="5">
         <v>6689</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="5">
         <v>6369</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="5">
         <v>4240</v>
       </c>
-      <c r="G20" s="4">
+      <c r="G20" s="5">
         <v>2417</v>
       </c>
-      <c r="H20" s="4">
+      <c r="H20" s="5">
         <v>2359</v>
       </c>
-      <c r="I20" s="4">
+      <c r="I20" s="5">
         <v>1984</v>
       </c>
     </row>
@@ -1336,61 +1358,61 @@
         <v>723</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="4" customFormat="1">
-      <c r="A29" s="4" t="s">
+    <row r="29" spans="1:9" s="5" customFormat="1">
+      <c r="A29" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="4">
+      <c r="B29" s="5">
         <v>62999</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C29" s="5">
         <v>57568</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29" s="5">
         <v>55892</v>
       </c>
-      <c r="E29" s="4">
+      <c r="E29" s="5">
         <v>54750</v>
       </c>
-      <c r="F29" s="4">
+      <c r="F29" s="5">
         <v>7497</v>
       </c>
-      <c r="G29" s="4">
+      <c r="G29" s="5">
         <v>5837</v>
       </c>
-      <c r="H29" s="4">
+      <c r="H29" s="5">
         <v>2827</v>
       </c>
-      <c r="I29" s="4">
+      <c r="I29" s="5">
         <v>1266</v>
       </c>
     </row>
-    <row r="30" spans="1:9" s="4" customFormat="1">
-      <c r="A30" s="4" t="s">
+    <row r="30" spans="1:9" s="5" customFormat="1">
+      <c r="A30" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B30" s="4">
+      <c r="B30" s="5">
         <v>76926</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C30" s="5">
         <v>69226</v>
       </c>
-      <c r="D30" s="4">
+      <c r="D30" s="5">
         <v>67885</v>
       </c>
-      <c r="E30" s="4">
+      <c r="E30" s="5">
         <v>67580</v>
       </c>
-      <c r="F30" s="4">
+      <c r="F30" s="5">
         <v>12419</v>
       </c>
-      <c r="G30" s="4">
+      <c r="G30" s="5">
         <v>8962</v>
       </c>
-      <c r="H30" s="4">
+      <c r="H30" s="5">
         <v>6028</v>
       </c>
-      <c r="I30" s="4">
+      <c r="I30" s="5">
         <v>4556</v>
       </c>
     </row>
@@ -1434,45 +1456,49 @@
   <sheetData>
     <row r="1" spans="1:10" ht="24" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="8" customHeight="1"/>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>38</v>
+      <c r="J3" s="4" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B4" s="1">
         <v>34639</v>
@@ -1504,7 +1530,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B5" s="1">
         <v>16456</v>
@@ -1534,64 +1560,64 @@
         <v>3466</v>
       </c>
     </row>
-    <row r="6" spans="1:10" s="4" customFormat="1">
-      <c r="A6" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="4">
+    <row r="6" spans="1:10" s="5" customFormat="1">
+      <c r="A6" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="5">
         <v>17487</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="5">
         <v>13060</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="5">
         <v>12220</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="5">
         <v>12998</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="5">
         <v>8505</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="5">
         <v>5416</v>
       </c>
     </row>
-    <row r="7" spans="1:10" s="4" customFormat="1">
-      <c r="A7" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B7" s="4">
+    <row r="7" spans="1:10" s="5" customFormat="1">
+      <c r="A7" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="5">
         <v>17152</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="5">
         <v>12725</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="5">
         <v>10460</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="5">
         <v>10603</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="5">
         <v>7929</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="5">
         <v>4347</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7" s="5">
         <v>2868</v>
       </c>
-      <c r="I7" s="4">
+      <c r="I7" s="5">
         <v>2447</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7" s="5">
         <v>1787</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B8" s="1">
         <v>8091</v>
@@ -1623,7 +1649,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B9" s="1">
         <v>4144</v>
@@ -1655,7 +1681,7 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B10" s="1">
         <v>1031</v>
@@ -1678,7 +1704,7 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" s="1">
         <v>-48</v>
@@ -1705,73 +1731,73 @@
         <v>-52</v>
       </c>
     </row>
-    <row r="12" spans="1:10" s="4" customFormat="1">
-      <c r="A12" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" s="4">
+    <row r="12" spans="1:10" s="5" customFormat="1">
+      <c r="A12" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="5">
         <v>13458</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="5">
         <v>10825</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="5">
         <v>10059</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="5">
         <v>9339</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="5">
         <v>4281</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G12" s="5">
         <v>2978</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H12" s="5">
         <v>2237</v>
       </c>
-      <c r="I12" s="4">
+      <c r="I12" s="5">
         <v>1996</v>
       </c>
-      <c r="J12" s="4">
+      <c r="J12" s="5">
         <v>1660</v>
       </c>
     </row>
-    <row r="13" spans="1:10" s="4" customFormat="1">
-      <c r="A13" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13" s="4">
+    <row r="13" spans="1:10" s="5" customFormat="1">
+      <c r="A13" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="5">
         <v>3694</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="5">
         <v>1900</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="5">
         <v>401</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="5">
         <v>1264</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="5">
         <v>3648</v>
       </c>
-      <c r="G13" s="4">
+      <c r="G13" s="5">
         <v>1369</v>
       </c>
-      <c r="H13" s="4">
+      <c r="H13" s="5">
         <v>631</v>
       </c>
-      <c r="I13" s="4">
+      <c r="I13" s="5">
         <v>451</v>
       </c>
-      <c r="J13" s="4">
+      <c r="J13" s="5">
         <v>127</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B14" s="1">
         <v>-131</v>
@@ -1803,7 +1829,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C15" s="1">
         <v>1989</v>
@@ -1827,35 +1853,35 @@
         <v>330</v>
       </c>
     </row>
-    <row r="16" spans="1:10" s="4" customFormat="1">
-      <c r="A16" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" s="4">
+    <row r="16" spans="1:10" s="5" customFormat="1">
+      <c r="A16" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="5">
         <v>2022</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="5">
         <v>508</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="5">
         <v>1198</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="5">
         <v>3675</v>
       </c>
-      <c r="G16" s="4">
+      <c r="G16" s="5">
         <v>1275</v>
       </c>
-      <c r="H16" s="4">
+      <c r="H16" s="5">
         <v>372</v>
       </c>
-      <c r="I16" s="4">
+      <c r="I16" s="5">
         <v>330</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B17" s="1">
         <v>26</v>
@@ -1879,41 +1905,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10" s="4" customFormat="1">
-      <c r="A18" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B18" s="4">
+    <row r="18" spans="1:10" s="5" customFormat="1">
+      <c r="A18" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" s="5">
         <v>4335</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18" s="5">
         <v>1641</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="5">
         <v>854</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="5">
         <v>1320</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="5">
         <v>3162</v>
       </c>
-      <c r="G18" s="4">
+      <c r="G18" s="5">
         <v>2490</v>
       </c>
-      <c r="H18" s="4">
+      <c r="H18" s="5">
         <v>341</v>
       </c>
-      <c r="I18" s="4">
+      <c r="I18" s="5">
         <v>337</v>
       </c>
-      <c r="J18" s="4">
+      <c r="J18" s="5">
         <v>-33</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B19" s="1">
         <v>2.63</v>
@@ -1945,7 +1971,7 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B20" s="1">
         <v>2.61</v>
@@ -1992,77 +2018,81 @@
   <sheetData>
     <row r="1" spans="1:10" ht="24" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="8" customHeight="1"/>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" s="4" customFormat="1">
-      <c r="A4" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B4" s="4">
+      <c r="J3" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" s="5" customFormat="1">
+      <c r="A4" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="5">
         <v>4335</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="5">
         <v>1641</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="5">
         <v>854</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="5">
         <v>1320</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="5">
         <v>3162</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="5">
         <v>2490</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="5">
         <v>341</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="5">
         <v>337</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="5">
         <v>-33</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B5" s="1">
         <v>750</v>
@@ -2094,7 +2124,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B6" s="1">
         <v>1638</v>
@@ -2126,7 +2156,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B7" s="1">
         <v>248</v>
@@ -2284,41 +2314,41 @@
         <v>-167</v>
       </c>
     </row>
-    <row r="12" spans="1:10" s="4" customFormat="1">
-      <c r="A12" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B12" s="4">
+    <row r="12" spans="1:10" s="5" customFormat="1">
+      <c r="A12" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="5">
         <v>6493</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="5">
         <v>3041</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="5">
         <v>1667</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="5">
         <v>3565</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="5">
         <v>3521</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G12" s="5">
         <v>1071</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H12" s="5">
         <v>493</v>
       </c>
-      <c r="I12" s="4">
+      <c r="I12" s="5">
         <v>34</v>
       </c>
-      <c r="J12" s="4">
+      <c r="J12" s="5">
         <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B13" s="1">
         <v>-974</v>
@@ -2348,84 +2378,84 @@
         <v>-113</v>
       </c>
     </row>
-    <row r="14" spans="1:10" s="4" customFormat="1">
-      <c r="A14" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B14" s="4">
+    <row r="14" spans="1:10" s="5" customFormat="1">
+      <c r="A14" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="5">
         <v>-6851</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="5">
         <v>-1101</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="5">
         <v>-1423</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="5">
         <v>-686</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G14" s="5">
         <v>-952</v>
       </c>
-      <c r="H14" s="4">
+      <c r="H14" s="5">
         <v>-149</v>
       </c>
-      <c r="I14" s="4">
+      <c r="I14" s="5">
         <v>-170</v>
       </c>
-      <c r="J14" s="4">
+      <c r="J14" s="5">
         <v>-54</v>
       </c>
     </row>
-    <row r="15" spans="1:10" s="4" customFormat="1">
-      <c r="A15" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E15" s="4">
+    <row r="15" spans="1:10" s="5" customFormat="1">
+      <c r="A15" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E15" s="5">
         <v>2300</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="5">
         <v>940</v>
       </c>
-      <c r="G15" s="4">
+      <c r="G15" s="5">
         <v>125</v>
       </c>
-      <c r="H15" s="4">
+      <c r="H15" s="5">
         <v>387</v>
       </c>
     </row>
-    <row r="16" spans="1:10" s="4" customFormat="1">
-      <c r="A16" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B16" s="4">
+    <row r="16" spans="1:10" s="5" customFormat="1">
+      <c r="A16" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" s="5">
         <v>-431</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="5">
         <v>-2062</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="5">
         <v>-1146</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="5">
         <v>-3264</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="5">
         <v>-1895</v>
       </c>
-      <c r="G16" s="4">
+      <c r="G16" s="5">
         <v>6</v>
       </c>
-      <c r="H16" s="4">
+      <c r="H16" s="5">
         <v>43</v>
       </c>
-      <c r="I16" s="4">
+      <c r="I16" s="5">
         <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B17" s="1">
         <v>2254</v>
@@ -2699,36 +2729,40 @@
   <sheetData>
     <row r="1" spans="1:9" ht="24" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="8" customHeight="1"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="18" customHeight="1">
+      <c r="A2" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2848,32 +2882,32 @@
         <v>7253</v>
       </c>
     </row>
-    <row r="8" spans="1:9" s="4" customFormat="1">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:9" s="5" customFormat="1">
+      <c r="A8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="5">
         <v>63688</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="5">
         <v>47324</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="5">
         <v>43269</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="5">
         <v>50407</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="5">
         <v>57718</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="5">
         <v>47249</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8" s="5">
         <v>31239</v>
       </c>
-      <c r="I8" s="4">
+      <c r="I8" s="5">
         <v>28787</v>
       </c>
     </row>
@@ -2908,7 +2942,7 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B10" s="1">
         <v>2772</v>
@@ -2935,32 +2969,32 @@
         <v>11836</v>
       </c>
     </row>
-    <row r="11" spans="1:9" s="4" customFormat="1">
-      <c r="A11" s="4" t="s">
+    <row r="11" spans="1:9" s="5" customFormat="1">
+      <c r="A11" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="5">
         <v>211429</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="5">
         <v>196485</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="5">
         <v>191572</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="5">
         <v>182103</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="5">
         <v>168406</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G11" s="5">
         <v>153091</v>
       </c>
-      <c r="H11" s="4">
+      <c r="H11" s="5">
         <v>136524</v>
       </c>
-      <c r="I11" s="4">
+      <c r="I11" s="5">
         <v>127963</v>
       </c>
     </row>
@@ -3022,32 +3056,32 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="14" spans="1:9" s="4" customFormat="1">
-      <c r="A14" s="4" t="s">
+    <row r="14" spans="1:9" s="5" customFormat="1">
+      <c r="A14" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="5">
         <v>31575</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="5">
         <v>35666</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="5">
         <v>28053</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="5">
         <v>32155</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="5">
         <v>27462</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G14" s="5">
         <v>24754</v>
       </c>
-      <c r="H14" s="4">
+      <c r="H14" s="5">
         <v>22310</v>
       </c>
-      <c r="I14" s="4">
+      <c r="I14" s="5">
         <v>16626</v>
       </c>
     </row>
@@ -3080,23 +3114,23 @@
         <v>2646</v>
       </c>
     </row>
-    <row r="16" spans="1:9" s="4" customFormat="1">
-      <c r="A16" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="G16" s="4">
+    <row r="16" spans="1:9" s="5" customFormat="1">
+      <c r="A16" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="G16" s="5">
         <v>153091</v>
       </c>
-      <c r="H16" s="4">
+      <c r="H16" s="5">
         <v>136524</v>
       </c>
-      <c r="I16" s="4">
+      <c r="I16" s="5">
         <v>127963</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B17" s="1">
         <v>0</v>
@@ -3210,61 +3244,61 @@
         <v>50172</v>
       </c>
     </row>
-    <row r="21" spans="1:9" s="4" customFormat="1">
-      <c r="A21" s="4" t="s">
+    <row r="21" spans="1:9" s="5" customFormat="1">
+      <c r="A21" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B21" s="5">
         <v>126360</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="5">
         <v>105032</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="5">
         <v>109965</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="5">
         <v>103286</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F21" s="5">
         <v>95391</v>
       </c>
-      <c r="G21" s="4">
+      <c r="G21" s="5">
         <v>81038</v>
       </c>
-      <c r="H21" s="4">
+      <c r="H21" s="5">
         <v>77504</v>
       </c>
-      <c r="I21" s="4">
+      <c r="I21" s="5">
         <v>74563</v>
       </c>
     </row>
-    <row r="22" spans="1:9" s="4" customFormat="1">
-      <c r="A22" s="4" t="s">
+    <row r="22" spans="1:9" s="5" customFormat="1">
+      <c r="A22" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B22" s="5">
         <v>211429</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="5">
         <v>196485</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="5">
         <v>191572</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E22" s="5">
         <v>182103</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F22" s="5">
         <v>168406</v>
       </c>
-      <c r="G22" s="4">
+      <c r="G22" s="5">
         <v>153091</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E23" s="1">
         <v>202</v>
@@ -3290,7 +3324,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="42.7109375" customWidth="1"/>
@@ -3299,45 +3333,49 @@
   <sheetData>
     <row r="1" spans="1:10" ht="24" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="8" customHeight="1"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>38</v>
+      <c r="J3" s="4" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B4" s="1">
         <v>52853</v>
@@ -3369,7 +3407,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B5" s="1">
         <v>34478</v>
@@ -3399,23 +3437,23 @@
         <v>23663</v>
       </c>
     </row>
-    <row r="6" spans="1:10" s="4" customFormat="1">
-      <c r="A6" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="4">
+    <row r="6" spans="1:10" s="5" customFormat="1">
+      <c r="A6" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="5">
         <v>18375</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="5">
         <v>17345</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="5">
         <v>21711</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7" s="1">
         <v>13774</v>
@@ -3447,7 +3485,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B8" s="1">
         <v>4624</v>
@@ -3479,7 +3517,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H9" s="1">
         <v>200</v>
@@ -3491,87 +3529,87 @@
         <v>177</v>
       </c>
     </row>
-    <row r="10" spans="1:10" s="4" customFormat="1">
-      <c r="A10" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" s="4">
+    <row r="10" spans="1:10" s="5" customFormat="1">
+      <c r="A10" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" s="5">
         <v>20589</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="5">
         <v>29023</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="5">
         <v>21618</v>
       </c>
     </row>
-    <row r="11" spans="1:10" s="4" customFormat="1">
-      <c r="A11" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B11" s="4">
+    <row r="11" spans="1:10" s="5" customFormat="1">
+      <c r="A11" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="5">
         <v>-2214</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="5">
         <v>-11678</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="5">
         <v>93</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="5">
         <v>2334</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="5">
         <v>19456</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G11" s="5">
         <v>23678</v>
       </c>
-      <c r="H11" s="4">
+      <c r="H11" s="5">
         <v>22035</v>
       </c>
-      <c r="I11" s="4">
+      <c r="I11" s="5">
         <v>23316</v>
       </c>
-      <c r="J11" s="4">
+      <c r="J11" s="5">
         <v>18050</v>
       </c>
     </row>
-    <row r="12" spans="1:10" s="4" customFormat="1">
-      <c r="A12" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B12" s="4">
+    <row r="12" spans="1:10" s="5" customFormat="1">
+      <c r="A12" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="5">
         <v>26</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="5">
         <v>-19233</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="5">
         <v>1675</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="5">
         <v>8017</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="5">
         <v>19868</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G12" s="5">
         <v>20899</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H12" s="5">
         <v>21048</v>
       </c>
-      <c r="I12" s="4">
+      <c r="I12" s="5">
         <v>21053</v>
       </c>
-      <c r="J12" s="4">
+      <c r="J12" s="5">
         <v>9601</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B13" s="1">
         <v>-0.06</v>
@@ -3603,7 +3641,7 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B14" s="1">
         <v>-0.06</v>
@@ -3635,7 +3673,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D15" s="1">
         <v>762</v>
@@ -3661,7 +3699,7 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E16" s="1">
         <v>3</v>
@@ -3673,8 +3711,39 @@
         <v>0</v>
       </c>
     </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>73</v>
+      </c>
+      <c r="F17" s="1">
+        <v>4059</v>
+      </c>
+      <c r="G17" s="1">
+        <v>4199</v>
+      </c>
+      <c r="H17" s="1">
+        <v>4417</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>74</v>
+      </c>
+      <c r="F18" s="1">
+        <v>4090</v>
+      </c>
+      <c r="G18" s="1">
+        <v>4232</v>
+      </c>
+      <c r="H18" s="1">
+        <v>4473</v>
+      </c>
+      <c r="I18" s="1">
+        <v>4701</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:J16"/>
+  <autoFilter ref="A3:J18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3690,77 +3759,81 @@
   <sheetData>
     <row r="1" spans="1:10" ht="24" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="8" customHeight="1"/>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" s="4" customFormat="1">
-      <c r="A4" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B4" s="4">
+      <c r="J3" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" s="5" customFormat="1">
+      <c r="A4" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="5">
         <v>26</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="5">
         <v>-19233</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="5">
         <v>1675</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="5">
         <v>8017</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="5">
         <v>19868</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="5">
         <v>20899</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="5">
         <v>21048</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="5">
         <v>21053</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="5">
         <v>9601</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B5" s="1">
         <v>10757</v>
@@ -3792,7 +3865,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B6" s="1">
         <v>2434</v>
@@ -3950,35 +4023,35 @@
         <v>-312</v>
       </c>
     </row>
-    <row r="11" spans="1:10" s="4" customFormat="1">
-      <c r="A11" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D11" s="4">
+    <row r="11" spans="1:10" s="5" customFormat="1">
+      <c r="A11" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" s="5">
         <v>11471</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="5">
         <v>15433</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="5">
         <v>29991</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G11" s="5">
         <v>35384</v>
       </c>
-      <c r="H11" s="4">
+      <c r="H11" s="5">
         <v>33145</v>
       </c>
-      <c r="I11" s="4">
+      <c r="I11" s="5">
         <v>29432</v>
       </c>
-      <c r="J11" s="4">
+      <c r="J11" s="5">
         <v>22110</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B12" s="1">
         <v>8249</v>
@@ -4141,39 +4214,43 @@
   <sheetData>
     <row r="1" spans="1:10" ht="24" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="8" customHeight="1"/>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="B3" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="4" t="s">
         <v>8</v>
       </c>
     </row>
@@ -4337,35 +4414,35 @@
         <v>136</v>
       </c>
     </row>
-    <row r="9" spans="1:10" s="4" customFormat="1">
-      <c r="A9" s="4" t="s">
+    <row r="9" spans="1:10" s="5" customFormat="1">
+      <c r="A9" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="5">
         <v>125605</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="5">
         <v>80126</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="5">
         <v>44345</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="5">
         <v>23073</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="5">
         <v>28829</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="5">
         <v>16055</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9" s="5">
         <v>13690</v>
       </c>
-      <c r="I9" s="4">
+      <c r="I9" s="5">
         <v>13690</v>
       </c>
-      <c r="J9" s="4">
+      <c r="J9" s="5">
         <v>10557</v>
       </c>
     </row>
@@ -4403,7 +4480,7 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B11" s="1">
         <v>2867</v>
@@ -4467,7 +4544,7 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B13" s="1">
         <v>3306</v>
@@ -4499,7 +4576,7 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B14" s="1">
         <v>13258</v>
@@ -4561,35 +4638,35 @@
         <v>108</v>
       </c>
     </row>
-    <row r="16" spans="1:10" s="4" customFormat="1">
-      <c r="A16" s="4" t="s">
+    <row r="16" spans="1:10" s="5" customFormat="1">
+      <c r="A16" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="5">
         <v>206803</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="5">
         <v>111601</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="5">
         <v>65728</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="5">
         <v>41182</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="5">
         <v>44187</v>
       </c>
-      <c r="G16" s="4">
+      <c r="G16" s="5">
         <v>28791</v>
       </c>
-      <c r="H16" s="4">
+      <c r="H16" s="5">
         <v>17315</v>
       </c>
-      <c r="I16" s="4">
+      <c r="I16" s="5">
         <v>17315</v>
       </c>
-      <c r="J16" s="4">
+      <c r="J16" s="5">
         <v>13292</v>
       </c>
     </row>
@@ -4627,7 +4704,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B18" s="1">
         <v>21352</v>
@@ -4680,35 +4757,35 @@
         <v>999</v>
       </c>
     </row>
-    <row r="20" spans="1:10" s="4" customFormat="1">
-      <c r="A20" s="4" t="s">
+    <row r="20" spans="1:10" s="5" customFormat="1">
+      <c r="A20" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" s="5">
         <v>32163</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="5">
         <v>18047</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="5">
         <v>10631</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="5">
         <v>6563</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="5">
         <v>4335</v>
       </c>
-      <c r="G20" s="4">
+      <c r="G20" s="5">
         <v>3925</v>
       </c>
-      <c r="H20" s="4">
+      <c r="H20" s="5">
         <v>1784</v>
       </c>
-      <c r="I20" s="4">
+      <c r="I20" s="5">
         <v>1784</v>
       </c>
-      <c r="J20" s="4">
+      <c r="J20" s="5">
         <v>1329</v>
       </c>
     </row>
@@ -4764,41 +4841,41 @@
         <v>1553</v>
       </c>
     </row>
-    <row r="23" spans="1:10" s="4" customFormat="1">
-      <c r="A23" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B23" s="4">
+    <row r="23" spans="1:10" s="5" customFormat="1">
+      <c r="A23" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" s="5">
         <v>49510</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C23" s="5">
         <v>32274</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="5">
         <v>22750</v>
       </c>
-      <c r="E23" s="4">
+      <c r="E23" s="5">
         <v>19081</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F23" s="5">
         <v>17575</v>
       </c>
-      <c r="G23" s="4">
+      <c r="G23" s="5">
         <v>11898</v>
       </c>
-      <c r="H23" s="4">
+      <c r="H23" s="5">
         <v>5111</v>
       </c>
-      <c r="I23" s="4">
+      <c r="I23" s="5">
         <v>5111</v>
       </c>
-      <c r="J23" s="4">
+      <c r="J23" s="5">
         <v>3950</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B24" s="1">
         <v>0</v>
@@ -4976,55 +5053,55 @@
         <v>12565</v>
       </c>
     </row>
-    <row r="30" spans="1:10" s="4" customFormat="1">
-      <c r="A30" s="4" t="s">
+    <row r="30" spans="1:10" s="5" customFormat="1">
+      <c r="A30" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B30" s="4">
+      <c r="B30" s="5">
         <v>157293</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C30" s="5">
         <v>79327</v>
       </c>
-      <c r="D30" s="4">
+      <c r="D30" s="5">
         <v>42978</v>
       </c>
-      <c r="E30" s="4">
+      <c r="E30" s="5">
         <v>22101</v>
       </c>
-      <c r="F30" s="4">
+      <c r="F30" s="5">
         <v>26612</v>
       </c>
-      <c r="G30" s="4">
+      <c r="G30" s="5">
         <v>16893</v>
       </c>
-      <c r="H30" s="4">
+      <c r="H30" s="5">
         <v>12204</v>
       </c>
-      <c r="I30" s="4">
+      <c r="I30" s="5">
         <v>12204</v>
       </c>
-      <c r="J30" s="4">
+      <c r="J30" s="5">
         <v>9342</v>
       </c>
     </row>
-    <row r="31" spans="1:10" s="4" customFormat="1">
-      <c r="A31" s="4" t="s">
+    <row r="31" spans="1:10" s="5" customFormat="1">
+      <c r="A31" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B31" s="4">
+      <c r="B31" s="5">
         <v>206803</v>
       </c>
-      <c r="C31" s="4">
+      <c r="C31" s="5">
         <v>111601</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D31" s="5">
         <v>65728</v>
       </c>
-      <c r="E31" s="4">
+      <c r="E31" s="5">
         <v>41182</v>
       </c>
-      <c r="F31" s="4">
+      <c r="F31" s="5">
         <v>44187</v>
       </c>
     </row>
@@ -5036,7 +5113,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="42.7109375" customWidth="1"/>
@@ -5045,48 +5122,52 @@
   <sheetData>
     <row r="1" spans="1:11" ht="24" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="8" customHeight="1"/>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="18" customHeight="1">
+      <c r="A2" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="B3" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>38</v>
+      <c r="K3" s="4" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B4" s="1">
         <v>25</v>
@@ -5121,7 +5202,7 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B5" s="1">
         <v>28.9</v>
@@ -5154,44 +5235,44 @@
         <v>3892</v>
       </c>
     </row>
-    <row r="6" spans="1:11" s="4" customFormat="1">
-      <c r="A6" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="4">
+    <row r="6" spans="1:11" s="5" customFormat="1">
+      <c r="A6" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="5">
         <v>71.09999999999999</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="5">
         <v>97858</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="5">
         <v>72.7</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="5">
         <v>15356</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="5">
         <v>17475</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="5">
         <v>62.3</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="5">
         <v>6768</v>
       </c>
-      <c r="I6" s="4">
+      <c r="I6" s="5">
         <v>6768</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="5">
         <v>7171</v>
       </c>
-      <c r="K6" s="4">
+      <c r="K6" s="5">
         <v>5822</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7" s="1">
         <v>8.6</v>
@@ -5224,79 +5305,79 @@
         <v>1797</v>
       </c>
     </row>
-    <row r="8" spans="1:11" s="4" customFormat="1">
-      <c r="A8" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" s="4">
+    <row r="8" spans="1:11" s="5" customFormat="1">
+      <c r="A8" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="5">
         <v>10.7</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="5">
         <v>16405</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="5">
         <v>18.6</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="5">
         <v>11132</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="5">
         <v>7434</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="5">
         <v>35.1</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8" s="5">
         <v>3922</v>
       </c>
-      <c r="I8" s="4">
+      <c r="I8" s="5">
         <v>3922</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J8" s="5">
         <v>3367</v>
       </c>
-      <c r="K8" s="4">
+      <c r="K8" s="5">
         <v>2612</v>
       </c>
     </row>
-    <row r="9" spans="1:11" s="4" customFormat="1">
-      <c r="A9" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" s="4">
+    <row r="9" spans="1:11" s="5" customFormat="1">
+      <c r="A9" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="5">
         <v>60.4</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="5">
         <v>81453</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="5">
         <v>54.1</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="5">
         <v>4224</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="5">
         <v>10041</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="5">
         <v>27.2</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9" s="5">
         <v>2846</v>
       </c>
-      <c r="I9" s="4">
+      <c r="I9" s="5">
         <v>2846</v>
       </c>
-      <c r="J9" s="4">
+      <c r="J9" s="5">
         <v>3804</v>
       </c>
-      <c r="K9" s="4">
+      <c r="K9" s="5">
         <v>3210</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B10" s="1">
         <v>1.1</v>
@@ -5331,7 +5412,7 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11" s="1">
         <v>-0.1</v>
@@ -5364,44 +5445,44 @@
         <v>-61</v>
       </c>
     </row>
-    <row r="12" spans="1:11" s="4" customFormat="1">
-      <c r="A12" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B12" s="4">
+    <row r="12" spans="1:11" s="5" customFormat="1">
+      <c r="A12" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="5">
         <v>141450</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="5">
         <v>84026</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="5">
         <v>33818</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="5">
         <v>4181</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="5">
         <v>9941</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G12" s="5">
         <v>4409</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H12" s="5">
         <v>2970</v>
       </c>
-      <c r="I12" s="4">
+      <c r="I12" s="5">
         <v>2970</v>
       </c>
-      <c r="J12" s="4">
+      <c r="J12" s="5">
         <v>3896</v>
       </c>
-      <c r="K12" s="4">
+      <c r="K12" s="5">
         <v>3196</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B13" s="1">
         <v>9.9</v>
@@ -5434,44 +5515,44 @@
         <v>149</v>
       </c>
     </row>
-    <row r="14" spans="1:11" s="4" customFormat="1">
-      <c r="A14" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B14" s="4">
+    <row r="14" spans="1:11" s="5" customFormat="1">
+      <c r="A14" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="5">
         <v>55.6</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="5">
         <v>72880</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="5">
         <v>48.9</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="5">
         <v>4368</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="5">
         <v>9752</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G14" s="5">
         <v>26</v>
       </c>
-      <c r="H14" s="4">
+      <c r="H14" s="5">
         <v>2796</v>
       </c>
-      <c r="I14" s="4">
+      <c r="I14" s="5">
         <v>2796</v>
       </c>
-      <c r="J14" s="4">
+      <c r="J14" s="5">
         <v>4141</v>
       </c>
-      <c r="K14" s="4">
+      <c r="K14" s="5">
         <v>3047</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B15" s="1">
         <v>4.93</v>
@@ -5506,7 +5587,7 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B16" s="1">
         <v>4.9</v>
@@ -5539,8 +5620,36 @@
         <v>4.82</v>
       </c>
     </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>73</v>
+      </c>
+      <c r="G17" s="1">
+        <v>617</v>
+      </c>
+      <c r="H17" s="1">
+        <v>2439</v>
+      </c>
+      <c r="I17" s="1">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>74</v>
+      </c>
+      <c r="G18" s="1">
+        <v>628</v>
+      </c>
+      <c r="H18" s="1">
+        <v>618</v>
+      </c>
+      <c r="I18" s="1">
+        <v>625</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:K16"/>
+  <autoFilter ref="A3:K18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5556,83 +5665,87 @@
   <sheetData>
     <row r="1" spans="1:11" ht="24" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="8" customHeight="1"/>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="18" customHeight="1">
+      <c r="A2" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="B3" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" s="4" customFormat="1">
-      <c r="A4" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B4" s="4">
+      <c r="K3" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="5" customFormat="1">
+      <c r="A4" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="5">
         <v>120067</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="5">
         <v>72880</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="5">
         <v>29760</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="5">
         <v>4368</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="5">
         <v>9752</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="5">
         <v>4332</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="5">
         <v>2796</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="5">
         <v>2796</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="5">
         <v>4141</v>
       </c>
-      <c r="K4" s="4">
+      <c r="K4" s="5">
         <v>3047</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B5" s="1">
         <v>2843</v>
@@ -5667,7 +5780,7 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B6" s="1">
         <v>6386</v>
@@ -5702,7 +5815,7 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B7" s="1">
         <v>-1424</v>
@@ -5875,32 +5988,32 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:11" s="4" customFormat="1">
-      <c r="A12" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B12" s="4">
+    <row r="12" spans="1:11" s="5" customFormat="1">
+      <c r="A12" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="5">
         <v>102718</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="5">
         <v>64089</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="5">
         <v>28090</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="5">
         <v>5641</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="5">
         <v>9108</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G12" s="5">
         <v>5822</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I13" s="1">
         <v>-489</v>
@@ -5912,63 +6025,63 @@
         <v>-593</v>
       </c>
     </row>
-    <row r="14" spans="1:11" s="4" customFormat="1">
-      <c r="A14" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B14" s="4">
+    <row r="14" spans="1:11" s="5" customFormat="1">
+      <c r="A14" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="5">
         <v>-52228</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="5">
         <v>-20421</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="5">
         <v>-10566</v>
       </c>
     </row>
-    <row r="15" spans="1:11" s="4" customFormat="1">
-      <c r="A15" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="B15" s="4">
+    <row r="15" spans="1:11" s="5" customFormat="1">
+      <c r="A15" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15" s="5">
         <v>10605</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="5">
         <v>8589</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="5">
         <v>7280</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="5">
         <v>3389</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="5">
         <v>1990</v>
       </c>
-      <c r="G15" s="4">
+      <c r="G15" s="5">
         <v>847</v>
       </c>
     </row>
-    <row r="16" spans="1:11" s="4" customFormat="1">
-      <c r="A16" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B16" s="4">
+    <row r="16" spans="1:11" s="5" customFormat="1">
+      <c r="A16" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" s="5">
         <v>-48474</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="5">
         <v>-42359</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="5">
         <v>-13633</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="5">
         <v>-11617</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B17" s="1">
         <v>5257</v>
